--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,12 +532,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -563,35 +564,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gr.-Qualifikation</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Sechzehntelfinale</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Achtelfinale</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Viertelfinale</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Halbfinale</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Platz 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Finale</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Weltmeister</t>
         </is>
@@ -633,6 +639,9 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -670,6 +679,9 @@
       <c r="K3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -705,6 +717,9 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,13 +532,12 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -569,35 +568,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Sechzehntelfinale</t>
+          <t>Achtelfinale</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Achtelfinale</t>
+          <t>Viertelfinale</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Viertelfinale</t>
+          <t>Halbfinale</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Halbfinale</t>
+          <t>Platz 3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Platz 3</t>
+          <t>Finale</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Finale</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Weltmeister</t>
         </is>
@@ -609,7 +603,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Test 2 Rathaus</t>
+          <t>Timo Test1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -637,9 +631,6 @@
         <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -649,7 +640,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Timo Test2</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -677,9 +668,6 @@
         <v>0</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -689,7 +677,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Timo Test</t>
+          <t>Timo Test2</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -717,9 +705,6 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -757,17 +742,17 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>Test 2 Rathaus</t>
+          <t>Timo Test1</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Timo Test2</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Timo Test</t>
+          <t>Timo Test2</t>
         </is>
       </c>
     </row>
@@ -791,17 +776,17 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>5:4</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -818,17 +803,17 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:5</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>4:2</t>
         </is>
       </c>
     </row>
@@ -845,17 +830,17 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -872,17 +857,17 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -899,17 +884,17 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>7:3</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>4:25</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:4</t>
         </is>
       </c>
     </row>
@@ -926,17 +911,17 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>7:8</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -960,17 +945,17 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -987,17 +972,17 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -1014,7 +999,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -1041,17 +1026,17 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1053,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:18</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
@@ -1078,7 +1063,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>3:3</t>
+          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -1095,17 +1080,17 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>6:8</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1114,17 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1141,17 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>0:6</t>
+          <t>8:8</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:5</t>
         </is>
       </c>
     </row>
@@ -1183,17 +1168,17 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:52</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1195,17 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>5:2</t>
+          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1222,17 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1264,17 +1249,17 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>8:84</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1298,17 +1283,17 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>8:1</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1310,12 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -1352,17 +1337,17 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:5</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1364,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5:8</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -1389,7 +1374,7 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>5:5</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1406,17 +1391,17 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>5:48</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1418,17 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:58</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1467,17 +1452,17 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1479,12 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1521,12 +1506,12 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:48</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -1548,17 +1533,17 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>5:8</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1575,17 +1560,17 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>0:6</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1587,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:8</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -1612,7 +1597,7 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1636,17 +1621,17 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5:8</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1663,17 +1648,17 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:8</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>0:02</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1690,17 +1675,17 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1702,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>4:5</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -1727,7 +1712,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1729,17 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1771,17 +1756,17 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1790,17 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1817,17 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1859,17 +1844,17 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1886,17 +1871,17 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1913,17 +1898,17 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>5:4</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1940,17 +1925,17 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1974,17 +1959,17 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2001,17 +1986,17 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2013,17 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:5</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2055,17 +2040,17 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2082,17 +2067,17 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:8</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2094,17 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2128,17 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:4</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2170,17 +2155,17 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2197,17 +2182,17 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2224,17 +2209,17 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>8:2</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2251,17 +2236,17 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:28</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2263,7 @@
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>8:4</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
@@ -2288,7 +2273,7 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2312,17 +2297,17 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2339,17 +2324,17 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:8</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2366,17 +2351,17 @@
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:4</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2378,17 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2405,17 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2432,17 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2481,17 +2466,17 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2493,12 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
@@ -2535,17 +2520,17 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:21</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2562,17 +2547,17 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2589,17 +2574,17 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2601,17 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2650,17 +2635,17 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:12</t>
         </is>
       </c>
     </row>
@@ -2677,17 +2662,17 @@
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2694,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2731,17 +2716,17 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>4:4</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2758,17 +2743,17 @@
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:21</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>4:5</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2770,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -2795,7 +2780,7 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>4:5</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2847,24 +2832,24 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>Test 2 Rathaus</t>
+          <t>Timo Test1</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Timo Test2</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Timo Test</t>
+          <t>Timo Test2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>── Sechzehntelfinale (je 5 Pkt.) ──</t>
+          <t>── Achtelfinale-Teilnehmer (16) (je 5 Pkt.) ──</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2871,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Mexiko</t>
+          <t>Kanada</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2913,12 +2898,12 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>Brasilien</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2920,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -2962,17 +2947,17 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Schweden</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2974,12 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Norwegen</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -3016,17 +3001,17 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Schottland</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Australien</t>
         </is>
       </c>
     </row>
@@ -3043,17 +3028,17 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Tschechien</t>
+          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -3070,17 +3055,17 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Kroatien</t>
         </is>
       </c>
     </row>
@@ -3097,17 +3082,17 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Ägypten</t>
+          <t>Belgien</t>
         </is>
       </c>
     </row>
@@ -3124,17 +3109,17 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
+          <t>Australien</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3141,12 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Argentinien</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Österreich</t>
+          <t>Jordanien</t>
         </is>
       </c>
     </row>
@@ -3178,17 +3163,17 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Kroatien</t>
+          <t>Kolumbien</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Kolumbien</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Kroatien</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -3205,17 +3190,17 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
           <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3217,17 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>Türkei</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -3259,17 +3244,17 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
+          <t>Jordanien</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Algerien</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -3286,24 +3271,24 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>── Achtelfinale (je 10 Pkt.) ──</t>
+          <t>── Viertelfinale-Teilnehmer (8) (je 10 Pkt.) ──</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3310,12 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Brasilien</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
@@ -3347,17 +3332,17 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Niederlande</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3359,17 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Norwegen</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Schottland</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Australien</t>
         </is>
       </c>
     </row>
@@ -3401,17 +3386,17 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Mexiko</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Tschechien</t>
+          <t>Kroatien</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3413,17 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Ägypten</t>
+          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3445,12 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Kroatien</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -3482,17 +3467,17 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Bosnien-Herzegowina</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>Ägypten</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -3509,24 +3494,24 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Argentinien</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Argentinien</t>
+          <t>Algerien</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>── Viertelfinale (je 15 Pkt.) ──</t>
+          <t>── Halbfinale-Teilnehmer (4) (je 15 Pkt.) ──</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3528,17 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Niederlande</t>
         </is>
       </c>
     </row>
@@ -3570,17 +3555,17 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Schottland</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Australien</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3582,17 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Kroatien</t>
+          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -3624,24 +3609,24 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Argentinien</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Argentinien</t>
+          <t>Ägypten</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>── Halbfinale (je 20 Pkt.) ──</t>
+          <t>── Finale (je 20 Pkt.) ──</t>
         </is>
       </c>
     </row>
@@ -3658,17 +3643,17 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Niederlande</t>
         </is>
       </c>
     </row>
@@ -3685,24 +3670,24 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Argentinien</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Ägypten</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>── Finale (beide Finalisten) (je 25 Pkt.) ──</t>
+          <t>── Weltmeister (je 25 Pkt.) ──</t>
         </is>
       </c>
     </row>
@@ -3719,84 +3704,22 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Weiterkommer 2</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>── Weltmeister (je 30 Pkt.) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Weiterkommer 1</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A39:E39"/>
+  <mergeCells count="5">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A33:E33"/>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Timo Test2</t>
+          <t>Timo Test3</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Timo Test2</t>
+          <t>Timo Test3</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Timo Test2</t>
+          <t>Timo Test3</t>
         </is>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -145,6 +145,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -524,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -603,7 +609,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Timo Test1</t>
+          <t>italien</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -640,7 +646,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Timo Test2</t>
+          <t>Timo Test1</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -677,7 +683,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Timo Test3</t>
+          <t>Timo Test2</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -705,6 +711,43 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Timo Test3</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -719,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -727,2058 +770,2424 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Spiel</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Ergebnis</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>italien</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Timo Test1</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Timo Test2</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Timo Test3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>── Gruppe A ──</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Mexiko vs Südafrika (11.06.)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>1:5</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>5:4</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>5:4</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Südkorea vs Tschechien (12.06.)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>1:5</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Tschechien vs Südafrika (18.06.)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Mexiko vs Südkorea (19.06.)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Tschechien vs Mexiko (25.06.)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>7:3</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>4:25</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>2:4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Südafrika vs Südkorea (25.06.)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>7:8</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>── Gruppe B ──</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Kanada vs Bosnien-Herzegowina (12.06.)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Katar vs Schweiz (13.06.)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Schweiz vs Bosnien-Herzegowina (18.06.)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Kanada vs Katar (19.06.)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Schweiz vs Kanada (24.06.)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>1:18</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina vs Katar (24.06.)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>6:8</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>── Gruppe C ──</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Brasilien vs Marokko (14.06.)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Haiti vs Schottland (14.06.)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>8:8</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>1:5</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Schottland vs Marokko (20.06.)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>4:4</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>1:52</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Brasilien vs Haiti (20.06.)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Schottland vs Brasilien (25.06.)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Marokko vs Haiti (25.06.)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>8:84</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>── Gruppe D ──</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>USA vs Paraguay (13.06.)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>8:1</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Australien vs Türkei (14.06.)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>USA vs Australien (19.06.)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Türkei vs Paraguay (20.06.)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>5:8</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Türkei vs USA (26.06.)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>5:48</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Paraguay vs Australien (26.06.)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>4:58</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>── Gruppe E ──</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Deutschland vs Curaçao (14.06.)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Elfenbeinküste vs Ecuador (15.06.)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>3:5</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>8:5</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Deutschland vs Elfenbeinküste (20.06.)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>4:48</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Ecuador vs Curaçao (21.06.)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>5:8</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Curaçao vs Elfenbeinküste (25.06.)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Ecuador vs Deutschland (25.06.)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>1:8</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>── Gruppe F ──</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Niederlande vs Japan (14.06.)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>5:8</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Schweden vs Tunesien (15.06.)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>1:8</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Niederlande vs Schweden (20.06.)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Tunesien vs Japan (21.06.)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Japan vs Schweden (26.06.)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Tunesien vs Niederlande (26.06.)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>8:5</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>── Gruppe G ──</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Belgien vs Ägypten (15.06.)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Iran vs Neuseeland (16.06.)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>4:4</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>1:21</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Belgien vs Iran (21.06.)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Neuseeland vs Ägypten (22.06.)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>8:5</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Ägypten vs Iran (27.06.)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>5:4</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Neuseeland vs Belgien (27.06.)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>8:5</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>── Gruppe H ──</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Spanien vs Kap Verde (15.06.)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Saudi-Arabien vs Uruguay (16.06.)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>2:5</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>8:5</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Spanien vs Saudi-Arabien (21.06.)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>4:5</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Uruguay vs Kap Verde (22.06.)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Kap Verde vs Saudi-Arabien (27.06.)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>2:8</t>
         </is>
       </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Uruguay vs Spanien (27.06.)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>1:21</t>
         </is>
       </c>
-      <c r="E57" s="15" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>── Gruppe I ──</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Frankreich vs Senegal (16.06.)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>2:4</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>Irak vs Norwegen (17.06.)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>Frankreich vs Irak (22.06.)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>1:21</t>
         </is>
       </c>
-      <c r="E61" s="15" t="inlineStr">
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Norwegen vs Senegal (23.06.)</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>8:2</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Norwegen vs Frankreich (26.06.)</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>4:28</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>Senegal vs Irak (26.06.)</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>8:4</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>── Gruppe J ──</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>Argentinien vs Algerien (17.06.)</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>Österreich vs Jordanien (17.06.)</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>4:8</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>Argentinien vs Österreich (22.06.)</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>2:4</t>
         </is>
       </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>Jordanien vs Algerien (23.06.)</t>
         </is>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E69" s="15" t="inlineStr">
+      <c r="F69" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>Algerien vs Österreich (28.06.)</t>
         </is>
       </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>Jordanien vs Argentinien (28.06.)</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>1:5</t>
         </is>
       </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>── Gruppe K ──</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>Portugal vs DR Kongo (17.06.)</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>5:1</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="F73" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" s="15" t="inlineStr">
         <is>
           <t>Usbekistan vs Kolumbien (18.06.)</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>Portugal vs Usbekistan (23.06.)</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>1:21</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="F75" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>Kolumbien vs DR Kongo (24.06.)</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr">
+      <c r="F76" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" s="15" t="inlineStr">
         <is>
           <t>Kolumbien vs Portugal (28.06.)</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="F77" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="A78" s="15" t="inlineStr">
         <is>
           <t>DR Kongo vs Usbekistan (28.06.)</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>── Gruppe L ──</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>England vs Kroatien (17.06.)</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
         <is>
           <t>2:12</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
+      <c r="A81" s="15" t="inlineStr">
         <is>
           <t>Ghana vs Panama (18.06.)</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E81" s="15" t="inlineStr">
+      <c r="F81" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>England vs Ghana (23.06.)</t>
         </is>
       </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>Panama vs Kroatien (24.06.)</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="A84" s="15" t="inlineStr">
         <is>
           <t>Panama vs England (27.06.)</t>
         </is>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>2:21</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E84" s="15" t="inlineStr">
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>Kroatien vs Ghana (27.06.)</t>
         </is>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E85" s="15" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -2786,18 +3195,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2809,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2817,902 +3226,1063 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>KO-Runde / Slot</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Tatsächlich</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>italien</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Timo Test1</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Timo Test2</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Timo Test3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>── Achtelfinale-Teilnehmer (16) (je 5 Pkt.) ──</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 1</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 2</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 3</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 4</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Schweden</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Schweden</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 5</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 6</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Schottland</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Australien</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 7</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 8</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 9</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 10</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Australien</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 11</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Österreich</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Jordanien</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 12</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 13</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 14</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 15</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Österreich</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Jordanien</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Algerien</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 16</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>── Viertelfinale-Teilnehmer (8) (je 10 Pkt.) ──</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 1</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 2</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 3</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Schottland</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Australien</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 4</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 5</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 6</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Österreich</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 7</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 8</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Österreich</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Algerien</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>── Halbfinale-Teilnehmer (4) (je 15 Pkt.) ──</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 1</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 2</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Schottland</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Australien</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 3</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 4</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>── Finale (je 20 Pkt.) ──</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 1</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 2</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>── Weltmeister (je 25 Pkt.) ──</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Weiterkommer 1</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
@@ -3720,11 +4290,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -535,7 +535,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
@@ -583,12 +583,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Finalisten (+20)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Platz 3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Finale</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -3626,7 +3626,7 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>── Finale (je 20 Pkt.) ──</t>
+          <t>── Finalisten (2) (je 20 Pkt.) ──</t>
         </is>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Egon Hejda</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Marco Schirmacher</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
@@ -794,34 +794,219 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
           <t>Timo Mayer</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7" t="n">
+      <c r="C12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -836,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -847,6 +1032,11 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,25 +1057,50 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Rony Burkart</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
         </is>
@@ -916,25 +1131,50 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -958,25 +1198,50 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -1000,25 +1265,50 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
@@ -1042,25 +1332,50 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
@@ -1089,20 +1404,45 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -1126,25 +1466,50 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -1175,25 +1540,50 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -1217,25 +1607,50 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -1269,15 +1684,40 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -1301,25 +1741,50 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -1343,25 +1808,50 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
@@ -1385,25 +1875,50 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -1434,12 +1949,12 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -1449,10 +1964,35 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
@@ -1476,25 +2016,50 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -1518,25 +2083,50 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="L19" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -1560,25 +2150,50 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
           <t>5:1</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="M20" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
@@ -1602,25 +2217,50 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -1644,25 +2284,50 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -1698,20 +2363,45 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
@@ -1730,30 +2420,55 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="L25" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="M25" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -1772,14 +2487,14 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
@@ -1787,15 +2502,40 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="M26" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -1819,25 +2559,50 @@
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -1856,30 +2621,55 @@
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="M28" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -1903,25 +2693,50 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="M29" s="17" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
@@ -1952,25 +2767,50 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
           <t>7:0</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
@@ -1989,7 +2829,7 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -1999,20 +2839,45 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
@@ -2041,20 +2906,45 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M33" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -2078,25 +2968,50 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
@@ -2120,25 +3035,50 @@
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
+          <t>0:7</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="M35" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2157,30 +3097,55 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>3:3</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -2211,25 +3176,50 @@
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M38" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -2253,7 +3243,7 @@
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="E39" s="17" t="inlineStr">
@@ -2263,15 +3253,40 @@
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="M39" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -2305,15 +3320,40 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
@@ -2342,20 +3382,45 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="I41" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="M41" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2379,25 +3444,50 @@
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M42" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
@@ -2421,25 +3511,50 @@
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="L43" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="M43" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2470,25 +3585,50 @@
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
@@ -2512,25 +3652,50 @@
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
         <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="K46" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="L46" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H46" s="17" t="inlineStr">
+      <c r="M46" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
@@ -2549,7 +3714,7 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -2573,6 +3738,31 @@
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M47" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -2591,30 +3781,55 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>3:3</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="I48" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="J48" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="K48" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L48" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H48" s="17" t="inlineStr">
+      <c r="M48" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -2638,25 +3853,50 @@
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="H49" s="17" t="inlineStr">
+      <c r="M49" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -2680,25 +3920,50 @@
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M50" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2734,20 +3999,45 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
           <t>6:0</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="L52" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="M52" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
@@ -2781,15 +4071,40 @@
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
+      <c r="L53" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="H53" s="17" t="inlineStr">
+      <c r="M53" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2813,25 +4128,50 @@
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="H54" s="17" t="inlineStr">
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -2855,25 +4195,50 @@
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="K55" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H55" s="17" t="inlineStr">
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
@@ -2892,30 +4257,55 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>1:4</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="F56" s="17" t="inlineStr">
+      <c r="K56" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="H56" s="17" t="inlineStr">
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -2939,25 +4329,50 @@
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="K57" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H57" s="17" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -2988,7 +4403,7 @@
       </c>
       <c r="D59" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E59" s="17" t="inlineStr">
@@ -3007,6 +4422,31 @@
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J59" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K59" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L59" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M59" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -3035,20 +4475,45 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="L60" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="M60" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -3072,25 +4537,50 @@
       </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K61" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="L61" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M61" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -3114,25 +4604,50 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J62" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="K62" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
+      <c r="L62" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="M62" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -3156,7 +4671,7 @@
       </c>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="E63" s="17" t="inlineStr">
@@ -3166,15 +4681,40 @@
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J63" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H63" s="17" t="inlineStr">
+      <c r="L63" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M63" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
@@ -3198,25 +4738,50 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
         <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M64" s="17" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
@@ -3257,15 +4822,40 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="L66" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="M66" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -3299,15 +4889,40 @@
       </c>
       <c r="F67" s="17" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H67" s="17" t="inlineStr">
+      <c r="L67" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M67" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -3331,25 +4946,50 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M68" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
@@ -3378,20 +5018,45 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="L69" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="M69" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
@@ -3415,25 +5080,50 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="K70" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
+      <c r="L70" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="M70" s="17" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
@@ -3457,25 +5147,50 @@
       </c>
       <c r="D71" s="17" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr">
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J71" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F71" s="17" t="inlineStr">
+      <c r="K71" s="17" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
+      <c r="L71" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="H71" s="17" t="inlineStr">
+      <c r="M71" s="17" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
@@ -3506,25 +5221,50 @@
       </c>
       <c r="D73" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="J73" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K73" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="H73" s="17" t="inlineStr">
+      <c r="L73" s="17" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="M73" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -3548,25 +5288,50 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="G74" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="F74" s="17" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="L74" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="M74" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
@@ -3590,12 +5355,12 @@
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
@@ -3605,10 +5370,35 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="H75" s="17" t="inlineStr">
+      <c r="J75" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K75" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="M75" s="17" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
@@ -3642,15 +5432,40 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J76" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L76" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M76" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -3674,25 +5489,50 @@
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J77" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F77" s="17" t="inlineStr">
+      <c r="K77" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G77" s="17" t="inlineStr">
+      <c r="L77" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
+      <c r="M77" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
@@ -3716,25 +5556,50 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="E78" s="17" t="inlineStr">
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="F78" s="17" t="inlineStr">
+      <c r="K78" s="17" t="inlineStr">
         <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr">
+      <c r="L78" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="M78" s="17" t="inlineStr">
         <is>
           <t>2:0</t>
         </is>
@@ -3765,25 +5630,50 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="E80" s="17" t="inlineStr">
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F80" s="17" t="inlineStr">
+      <c r="K80" s="17" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H80" s="17" t="inlineStr">
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M80" s="17" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
@@ -3807,25 +5697,50 @@
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="E81" s="17" t="inlineStr">
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J81" s="17" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H81" s="17" t="inlineStr">
+      <c r="K81" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L81" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M81" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
@@ -3849,25 +5764,50 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F82" s="17" t="inlineStr">
+      <c r="K82" s="17" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H82" s="17" t="inlineStr">
+      <c r="L82" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M82" s="17" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
@@ -3891,25 +5831,50 @@
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="E83" s="17" t="inlineStr">
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J83" s="17" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F83" s="17" t="inlineStr">
+      <c r="K83" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G83" s="17" t="inlineStr">
+      <c r="L83" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H83" s="17" t="inlineStr">
+      <c r="M83" s="17" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
@@ -3933,25 +5898,50 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E84" s="17" t="inlineStr">
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="F84" s="17" t="inlineStr">
+      <c r="K84" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="H84" s="17" t="inlineStr">
+      <c r="L84" s="17" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M84" s="17" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
@@ -3975,25 +5965,50 @@
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="E85" s="17" t="inlineStr">
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H85" s="17" t="inlineStr">
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M85" s="17" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
@@ -4001,18 +6016,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A44:M44"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A79:M79"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A65:M65"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A51:M51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4024,7 +6039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4035,6 +6050,11 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4055,25 +6075,50 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Rony Burkart</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
         </is>
@@ -4099,30 +6144,55 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
@@ -4156,15 +6226,40 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
@@ -4193,20 +6288,45 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
@@ -4240,15 +6360,40 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
@@ -4267,30 +6412,55 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
@@ -4314,25 +6484,50 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -4351,7 +6546,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Mexiko</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -4361,20 +6556,45 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Mexiko</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -4398,25 +6618,50 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -4445,7 +6690,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>Ägypten</t>
+          <t>Belgien</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -4459,6 +6704,31 @@
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
@@ -4477,30 +6747,55 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
@@ -4547,6 +6842,31 @@
           <t>Spanien</t>
         </is>
       </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -4566,25 +6886,50 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
@@ -4628,6 +6973,31 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
+        <is>
           <t>Kanada</t>
         </is>
       </c>
@@ -4645,30 +7015,55 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
@@ -4715,6 +7110,31 @@
           <t>Argentinien</t>
         </is>
       </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -4757,6 +7177,31 @@
           <t>Portugal</t>
         </is>
       </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -4778,30 +7223,55 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -4820,30 +7290,55 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="L21" s="17" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
@@ -4862,30 +7357,55 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
@@ -4909,25 +7429,50 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -4946,30 +7491,55 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -4988,30 +7558,55 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="L25" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
@@ -5030,30 +7625,55 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -5072,30 +7692,55 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5126,25 +7771,50 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -5163,30 +7833,55 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="L30" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -5205,30 +7900,55 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -5257,20 +7977,45 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -5296,30 +8041,55 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -5338,30 +8108,55 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="M35" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -5397,20 +8192,45 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="M37" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -5418,11 +8238,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -6251,7 +6251,7 @@
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>Niederlande</t>
+          <t>Brasilien</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>Niederlande</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="L20" s="17" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Mexiko</t>
         </is>
       </c>
       <c r="L21" s="17" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Brasilien</t>
         </is>
       </c>
       <c r="L22" s="17" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Türkei</t>
         </is>
       </c>
       <c r="L25" s="17" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>Schweiz</t>
+          <t>Argentinien</t>
         </is>
       </c>
       <c r="L26" s="17" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="L30" s="17" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>England</t>
         </is>
       </c>
       <c r="L31" s="17" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="K35" s="17" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>England</t>
         </is>
       </c>
       <c r="L35" s="17" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -826,14 +826,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Egon Hejda</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Egon Hejda</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
@@ -937,14 +937,14 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Heiko Baust</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Heiko Baust</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
@@ -1147,37 +1147,37 @@
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
           <t>Egon Hejda</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Heiko Baust</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
     </row>
@@ -1224,39 +1224,39 @@
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
     </row>
@@ -1298,37 +1298,37 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K4" s="20" t="inlineStr">
+      <c r="M4" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="inlineStr">
+      <c r="N4" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
     </row>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1586,37 +1586,37 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -1665,37 +1665,37 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -1737,37 +1737,37 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="M11" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
         </is>
       </c>
     </row>
@@ -1809,37 +1809,37 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1881,37 +1881,37 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1953,37 +1953,37 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -2035,27 +2035,27 @@
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="M15" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="M18" s="21" t="inlineStr">
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
         </is>
       </c>
     </row>
@@ -2248,37 +2248,37 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -2325,32 +2325,32 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>5:1</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2397,32 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -2543,14 +2543,14 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
@@ -2558,17 +2558,17 @@
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -2620,32 +2620,32 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -2687,37 +2687,37 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J26" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>3:3</t>
         </is>
       </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N26" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2759,37 +2759,37 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
+      <c r="N27" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="K28" s="21" t="inlineStr">
+      <c r="M28" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr">
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2903,37 +2903,37 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="M29" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
+      <c r="N29" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2982,37 +2982,37 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J31" s="21" t="inlineStr">
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K31" s="21" t="inlineStr">
+      <c r="M31" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
+      <c r="N31" s="21" t="inlineStr">
         <is>
           <t>7:0</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -3054,32 +3054,32 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -3126,37 +3126,37 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="M33" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N33" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>5:0</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
     </row>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K35" s="21" t="inlineStr">
+      <c r="M35" s="21" t="inlineStr">
         <is>
           <t>0:0</t>
-        </is>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N35" s="21" t="inlineStr">
@@ -3342,37 +3342,37 @@
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="J36" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J36" s="21" t="inlineStr">
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K36" s="21" t="inlineStr">
+      <c r="M36" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N36" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -3421,37 +3421,37 @@
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="L38" s="21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N38" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3493,27 +3493,27 @@
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J39" s="21" t="inlineStr">
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="K39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L39" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="I40" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="J40" s="21" t="inlineStr">
@@ -3580,22 +3580,22 @@
       </c>
       <c r="K40" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="L40" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N40" s="21" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3637,32 +3637,32 @@
       </c>
       <c r="H41" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I41" s="21" t="inlineStr">
+      <c r="J41" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J41" s="21" t="inlineStr">
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K41" s="21" t="inlineStr">
+      <c r="M41" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
       <c r="N41" s="21" t="inlineStr">
@@ -3709,32 +3709,32 @@
       </c>
       <c r="H42" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J42" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K42" s="21" t="inlineStr">
+      <c r="L42" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M42" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
       <c r="N42" s="21" t="inlineStr">
@@ -3781,37 +3781,37 @@
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I43" s="21" t="inlineStr">
+      <c r="J43" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J43" s="21" t="inlineStr">
+      <c r="K43" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="L43" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K43" s="21" t="inlineStr">
+      <c r="M43" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="L43" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M43" s="21" t="inlineStr">
+      <c r="N43" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
-        </is>
-      </c>
-      <c r="N43" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
         </is>
       </c>
     </row>
@@ -3860,14 +3860,14 @@
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
@@ -3875,22 +3875,22 @@
       </c>
       <c r="K45" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="L45" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N45" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="N45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3932,32 @@
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J46" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K46" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K46" s="21" t="inlineStr">
+      <c r="L46" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M46" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M46" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
       <c r="N46" s="21" t="inlineStr">
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J47" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K47" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="L47" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M47" s="21" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="N47" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4076,37 +4076,37 @@
       </c>
       <c r="H48" s="21" t="inlineStr">
         <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="I48" s="21" t="inlineStr">
+      <c r="J48" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="J48" s="21" t="inlineStr">
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K48" s="21" t="inlineStr">
+      <c r="M48" s="21" t="inlineStr">
         <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="M48" s="21" t="inlineStr">
+      <c r="N48" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N48" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I49" s="21" t="inlineStr">
@@ -4158,27 +4158,27 @@
       </c>
       <c r="J49" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K49" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L49" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="K49" s="21" t="inlineStr">
+      <c r="M49" s="21" t="inlineStr">
         <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="L49" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M49" s="21" t="inlineStr">
+      <c r="N49" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="N49" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -4220,32 +4220,32 @@
       </c>
       <c r="H50" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I50" s="21" t="inlineStr">
+      <c r="J50" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J50" s="21" t="inlineStr">
+      <c r="K50" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L50" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K50" s="21" t="inlineStr">
+      <c r="M50" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="L50" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M50" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N50" s="21" t="inlineStr">
@@ -4299,37 +4299,37 @@
       </c>
       <c r="H52" s="21" t="inlineStr">
         <is>
+          <t>7:0</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I52" s="21" t="inlineStr">
+      <c r="J52" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="J52" s="21" t="inlineStr">
+      <c r="K52" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L52" s="21" t="inlineStr">
         <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="K52" s="21" t="inlineStr">
+      <c r="M52" s="21" t="inlineStr">
         <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>7:0</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
+      <c r="N52" s="21" t="inlineStr">
         <is>
           <t>6:0</t>
-        </is>
-      </c>
-      <c r="N52" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4376,32 @@
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J53" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J53" s="21" t="inlineStr">
+      <c r="K53" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="K53" s="21" t="inlineStr">
+      <c r="M53" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="L53" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M53" s="21" t="inlineStr">
+      <c r="N53" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
-        </is>
-      </c>
-      <c r="N53" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
       </c>
       <c r="H54" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I54" s="21" t="inlineStr">
+      <c r="J54" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="J54" s="21" t="inlineStr">
+      <c r="K54" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K54" s="21" t="inlineStr">
+      <c r="L54" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M54" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="L54" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M54" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N54" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
           <t>2:0</t>
@@ -4530,22 +4530,22 @@
       </c>
       <c r="K55" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="L55" s="21" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M55" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N55" s="21" t="inlineStr">
+        <is>
           <t>5:0</t>
-        </is>
-      </c>
-      <c r="N55" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -4592,32 +4592,32 @@
       </c>
       <c r="I56" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J56" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J56" s="21" t="inlineStr">
+      <c r="K56" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K56" s="21" t="inlineStr">
+      <c r="M56" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="L56" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M56" s="21" t="inlineStr">
+      <c r="N56" s="21" t="inlineStr">
         <is>
           <t>0:4</t>
-        </is>
-      </c>
-      <c r="N56" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -4659,32 +4659,32 @@
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I57" s="21" t="inlineStr">
+      <c r="J57" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J57" s="21" t="inlineStr">
+      <c r="K57" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K57" s="21" t="inlineStr">
+      <c r="M57" s="21" t="inlineStr">
         <is>
           <t>1:4</t>
-        </is>
-      </c>
-      <c r="L57" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
-        </is>
-      </c>
-      <c r="M57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
       <c r="N57" s="21" t="inlineStr">
@@ -4738,37 +4738,37 @@
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J59" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="J59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K59" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M59" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="L59" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="M59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N59" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I60" s="21" t="inlineStr">
+      <c r="J60" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J60" s="21" t="inlineStr">
+      <c r="K60" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L60" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="K60" s="21" t="inlineStr">
+      <c r="M60" s="21" t="inlineStr">
         <is>
           <t>1:4</t>
-        </is>
-      </c>
-      <c r="L60" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M60" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N60" s="21" t="inlineStr">
@@ -4882,37 +4882,37 @@
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I61" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="I61" s="21" t="inlineStr">
+      <c r="J61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J61" s="21" t="inlineStr">
+      <c r="K61" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K61" s="21" t="inlineStr">
+      <c r="M61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="L61" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M61" s="21" t="inlineStr">
+      <c r="N61" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="N61" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H62" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="I62" s="21" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="J62" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K62" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K62" s="21" t="inlineStr">
+      <c r="L62" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="M62" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="L62" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M62" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N62" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5026,37 +5026,37 @@
       </c>
       <c r="H63" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I63" s="21" t="inlineStr">
+      <c r="J63" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J63" s="21" t="inlineStr">
+      <c r="K63" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K63" s="21" t="inlineStr">
+      <c r="L63" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M63" s="21" t="inlineStr">
         <is>
           <t>1:4</t>
         </is>
       </c>
-      <c r="L63" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M63" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N63" s="21" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -5098,37 +5098,37 @@
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I64" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J64" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K64" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="L64" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="L64" s="21" t="inlineStr">
-        <is>
-          <t>5:2</t>
-        </is>
-      </c>
-      <c r="M64" s="21" t="inlineStr">
+      <c r="N64" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="N64" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
     </row>
@@ -5177,37 +5177,37 @@
       </c>
       <c r="H66" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I66" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J66" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="J66" s="21" t="inlineStr">
+      <c r="K66" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L66" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K66" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L66" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
       <c r="M66" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N66" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5249,37 +5249,37 @@
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J67" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K67" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="L67" s="21" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M67" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N67" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="N67" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -5321,19 +5321,19 @@
       </c>
       <c r="H68" s="21" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I68" s="21" t="inlineStr">
+      <c r="J68" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J68" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="K68" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
@@ -5341,17 +5341,17 @@
       </c>
       <c r="L68" s="21" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="M68" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="N68" s="21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="J69" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K69" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="K69" s="21" t="inlineStr">
+      <c r="M69" s="21" t="inlineStr">
         <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="L69" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M69" s="21" t="inlineStr">
+      <c r="N69" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
-        </is>
-      </c>
-      <c r="N69" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5465,27 +5465,27 @@
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I70" s="21" t="inlineStr">
+      <c r="J70" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J70" s="21" t="inlineStr">
+      <c r="K70" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L70" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="K70" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L70" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
         </is>
       </c>
       <c r="M70" s="21" t="inlineStr">
@@ -5537,37 +5537,37 @@
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I71" s="21" t="inlineStr">
+      <c r="J71" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="J71" s="21" t="inlineStr">
+      <c r="K71" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="L71" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="K71" s="21" t="inlineStr">
+      <c r="M71" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="L71" s="21" t="inlineStr">
-        <is>
-          <t>0:5</t>
-        </is>
-      </c>
-      <c r="M71" s="21" t="inlineStr">
+      <c r="N71" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="N71" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
         </is>
       </c>
     </row>
@@ -5616,37 +5616,37 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="I73" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J73" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K73" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L73" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="K73" s="21" t="inlineStr">
+      <c r="M73" s="21" t="inlineStr">
         <is>
           <t>5:1</t>
         </is>
       </c>
-      <c r="L73" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M73" s="21" t="inlineStr">
+      <c r="N73" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="N73" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5693,32 @@
       </c>
       <c r="I74" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J74" s="21" t="inlineStr">
+      <c r="K74" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L74" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K74" s="21" t="inlineStr">
+      <c r="M74" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="L74" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M74" s="21" t="inlineStr">
+      <c r="N74" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="N74" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -5760,37 +5760,37 @@
       </c>
       <c r="H75" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I75" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="I75" s="21" t="inlineStr">
+      <c r="J75" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J75" s="21" t="inlineStr">
+      <c r="K75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L75" s="21" t="inlineStr">
         <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="K75" s="21" t="inlineStr">
+      <c r="M75" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="L75" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M75" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N75" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5832,32 @@
       </c>
       <c r="H76" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I76" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J76" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="J76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K76" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M76" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L76" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="M76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
       <c r="N76" s="21" t="inlineStr">
@@ -5909,32 +5909,32 @@
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J77" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J77" s="21" t="inlineStr">
+      <c r="K77" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L77" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K77" s="21" t="inlineStr">
+      <c r="M77" s="21" t="inlineStr">
         <is>
           <t>1:4</t>
         </is>
       </c>
-      <c r="L77" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M77" s="21" t="inlineStr">
+      <c r="N77" s="21" t="inlineStr">
         <is>
           <t>0:0</t>
-        </is>
-      </c>
-      <c r="N77" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5976,32 +5976,32 @@
       </c>
       <c r="H78" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I78" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J78" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J78" s="21" t="inlineStr">
+      <c r="K78" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="L78" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K78" s="21" t="inlineStr">
+      <c r="M78" s="21" t="inlineStr">
         <is>
           <t>3:2</t>
-        </is>
-      </c>
-      <c r="L78" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="M78" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
       <c r="N78" s="21" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I80" s="21" t="inlineStr">
@@ -6065,27 +6065,27 @@
       </c>
       <c r="J80" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K80" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L80" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M80" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="L80" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M80" s="21" t="inlineStr">
+      <c r="N80" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="N80" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="J81" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K81" s="21" t="inlineStr">
@@ -6147,17 +6147,17 @@
       </c>
       <c r="L81" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N81" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="N81" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I82" s="21" t="inlineStr">
@@ -6209,27 +6209,27 @@
       </c>
       <c r="J82" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K82" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L82" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M82" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="L82" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M82" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N82" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -6271,32 +6271,32 @@
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I83" s="21" t="inlineStr">
+      <c r="J83" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J83" s="21" t="inlineStr">
+      <c r="K83" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K83" s="21" t="inlineStr">
+      <c r="M83" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="L83" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="M83" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
       <c r="N83" s="21" t="inlineStr">
@@ -6343,32 +6343,32 @@
       </c>
       <c r="H84" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I84" s="21" t="inlineStr">
+      <c r="J84" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="J84" s="21" t="inlineStr">
+      <c r="K84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L84" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="K84" s="21" t="inlineStr">
+      <c r="M84" s="21" t="inlineStr">
         <is>
           <t>1:4</t>
-        </is>
-      </c>
-      <c r="L84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N84" s="21" t="inlineStr">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="H85" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I85" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I85" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="J85" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
@@ -6430,22 +6430,22 @@
       </c>
       <c r="K85" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L85" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M85" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="L85" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M85" s="21" t="inlineStr">
+      <c r="N85" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="N85" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -6531,37 +6531,37 @@
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
           <t>Egon Hejda</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Heiko Baust</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="M3" s="21" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="M3" s="21" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -6908,27 +6908,27 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="M8" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
     </row>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="M10" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
     </row>
@@ -7258,37 +7258,37 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -7402,37 +7402,37 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
     </row>
@@ -7546,37 +7546,37 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>Neuseeland</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -7769,37 +7769,37 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -7841,37 +7841,37 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -7913,37 +7913,37 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
     </row>
@@ -8057,37 +8057,37 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
+      <c r="M24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M24" s="21" t="inlineStr">
+      <c r="N24" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -8129,37 +8129,37 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -8201,37 +8201,37 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="L26" s="21" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="M26" s="21" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
     </row>
@@ -8278,32 +8278,32 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="M27" s="21" t="inlineStr">
+      <c r="N27" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -8362,27 +8362,27 @@
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="M29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
+      <c r="N29" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -8424,37 +8424,37 @@
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K30" s="21" t="inlineStr">
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L30" s="21" t="inlineStr">
+      <c r="M30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M30" s="21" t="inlineStr">
+      <c r="N30" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="N30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -8496,37 +8496,37 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J31" s="21" t="inlineStr">
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="K31" s="21" t="inlineStr">
+      <c r="M31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
+      <c r="N31" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
     </row>
@@ -8568,37 +8568,37 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L32" s="21" t="inlineStr">
+      <c r="N32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -8647,37 +8647,37 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K34" s="21" t="inlineStr">
+      <c r="M34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -8719,37 +8719,37 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K35" s="21" t="inlineStr">
+      <c r="M35" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
+      <c r="N35" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,32 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K37" s="21" t="inlineStr">
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L37" s="21" t="inlineStr">
+      <c r="N37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -826,14 +826,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Egon Hejda</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Egon Hejda</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
@@ -937,14 +937,14 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Heiko Baust</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Heiko Baust</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
@@ -1147,37 +1147,37 @@
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Heiko Baust</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Egon Hejda</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Heiko Baust</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
         </is>
       </c>
     </row>
@@ -1224,39 +1224,39 @@
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K3" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="M3" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
     </row>
@@ -1298,14 +1298,14 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
@@ -1313,22 +1313,22 @@
       </c>
       <c r="K4" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
     </row>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:2</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
         <is>
-          <t>4:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -1586,37 +1586,37 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1665,37 +1665,37 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1737,37 +1737,37 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t>0:4</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -1809,37 +1809,37 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1881,37 +1881,37 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1953,37 +1953,37 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
     </row>
@@ -2025,37 +2025,37 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2109,32 +2109,32 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="M17" s="21" t="inlineStr">
         <is>
-          <t>4:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
           <t>0:4</t>
-        </is>
-      </c>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -2248,37 +2248,37 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K19" s="21" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -2325,32 +2325,32 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>5:1</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2397,32 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
         </is>
       </c>
     </row>
@@ -2543,32 +2543,32 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -2620,32 +2620,32 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -2687,37 +2687,37 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>3:3</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2759,37 +2759,37 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
           <t>2:4</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
       <c r="N28" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2903,37 +2903,37 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2982,37 +2982,37 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>7:0</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>7:0</t>
         </is>
       </c>
     </row>
@@ -3054,32 +3054,32 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -3126,37 +3126,37 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K33" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="N33" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3198,37 +3198,37 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
         </is>
       </c>
     </row>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
       <c r="N35" s="21" t="inlineStr">
@@ -3342,37 +3342,37 @@
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J36" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K36" s="21" t="inlineStr">
+      <c r="M36" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N36" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3421,37 +3421,37 @@
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="J38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K38" s="21" t="inlineStr">
+      <c r="M38" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N38" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L38" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N38" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3493,27 +3493,27 @@
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J39" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L39" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="I40" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="J40" s="21" t="inlineStr">
@@ -3580,22 +3580,22 @@
       </c>
       <c r="K40" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="inlineStr">
+        <is>
           <t>0:0</t>
-        </is>
-      </c>
-      <c r="L40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3637,32 +3637,32 @@
       </c>
       <c r="H41" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K41" s="21" t="inlineStr">
+      <c r="M41" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
       <c r="N41" s="21" t="inlineStr">
@@ -3709,32 +3709,32 @@
       </c>
       <c r="H42" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L42" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I42" s="21" t="inlineStr">
+      <c r="M42" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="J42" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
       <c r="N42" s="21" t="inlineStr">
@@ -3781,37 +3781,37 @@
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K43" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="inlineStr">
+      <c r="L43" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M43" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="N43" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="L43" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M43" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N43" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
         </is>
       </c>
     </row>
@@ -3860,37 +3860,37 @@
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J45" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K45" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L45" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="N45" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3932,32 @@
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I46" s="21" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="J46" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K46" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M46" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M46" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
       <c r="N46" s="21" t="inlineStr">
@@ -4004,37 +4004,37 @@
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J47" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K47" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L47" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K47" s="21" t="inlineStr">
+      <c r="M47" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N47" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="L47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4076,37 +4076,37 @@
       </c>
       <c r="H48" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="J48" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
+        <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="inlineStr">
+      <c r="M48" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="N48" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M48" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="N48" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -4148,37 +4148,37 @@
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K49" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="L49" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J49" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K49" s="21" t="inlineStr">
+      <c r="M49" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="N49" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L49" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="M49" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="N49" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
     </row>
@@ -4220,32 +4220,32 @@
       </c>
       <c r="H50" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I50" s="21" t="inlineStr">
+      <c r="J50" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K50" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="L50" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M50" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="J50" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K50" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L50" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M50" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
         </is>
       </c>
       <c r="N50" s="21" t="inlineStr">
@@ -4299,37 +4299,37 @@
       </c>
       <c r="H52" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="J52" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="K52" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="L52" s="21" t="inlineStr">
+        <is>
           <t>7:0</t>
         </is>
       </c>
-      <c r="I52" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="J52" s="21" t="inlineStr">
+      <c r="M52" s="21" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="N52" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="N52" s="21" t="inlineStr">
-        <is>
-          <t>6:0</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4376,32 @@
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J53" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="K53" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J53" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K53" s="21" t="inlineStr">
+      <c r="M53" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="N53" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="L53" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M53" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N53" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
       </c>
       <c r="H54" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I54" s="21" t="inlineStr">
+      <c r="J54" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J54" s="21" t="inlineStr">
+      <c r="K54" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L54" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="K54" s="21" t="inlineStr">
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N54" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="L54" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M54" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="N54" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -4515,37 +4515,37 @@
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J55" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K55" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L55" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J55" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K55" s="21" t="inlineStr">
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="N55" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="L55" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M55" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N55" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
         </is>
       </c>
     </row>
@@ -4592,32 +4592,32 @@
       </c>
       <c r="I56" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J56" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="J56" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
       <c r="K56" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M56" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="N56" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L56" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M56" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="N56" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
         </is>
       </c>
     </row>
@@ -4659,32 +4659,32 @@
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J57" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K57" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
+        <is>
           <t>2:4</t>
         </is>
       </c>
-      <c r="I57" s="21" t="inlineStr">
+      <c r="M57" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="J57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="L57" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M57" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
         </is>
       </c>
       <c r="N57" s="21" t="inlineStr">
@@ -4738,37 +4738,37 @@
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I59" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K59" s="21" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
+        <is>
           <t>4:2</t>
         </is>
       </c>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
+      <c r="M59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N59" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="K59" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="L59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M59" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="N59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J60" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="I60" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J60" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
       <c r="K60" s="21" t="inlineStr">
         <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="L60" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="M60" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="L60" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M60" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
         </is>
       </c>
       <c r="N60" s="21" t="inlineStr">
@@ -4882,37 +4882,37 @@
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I61" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I61" s="21" t="inlineStr">
+      <c r="J61" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K61" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L61" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M61" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="N61" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="J61" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="K61" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L61" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M61" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="N61" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -4954,37 +4954,37 @@
       </c>
       <c r="H62" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I62" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J62" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K62" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L62" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I62" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J62" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K62" s="21" t="inlineStr">
+      <c r="M62" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N62" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L62" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M62" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="N62" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5026,37 +5026,37 @@
       </c>
       <c r="H63" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J63" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K63" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="L63" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I63" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="J63" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K63" s="21" t="inlineStr">
+      <c r="M63" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N63" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="L63" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M63" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="N63" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -5098,37 +5098,37 @@
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J64" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K64" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L64" s="21" t="inlineStr">
+        <is>
           <t>5:2</t>
         </is>
       </c>
-      <c r="I64" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="J64" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K64" s="21" t="inlineStr">
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="N64" s="21" t="inlineStr">
         <is>
           <t>0:0</t>
-        </is>
-      </c>
-      <c r="L64" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M64" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="N64" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5177,37 +5177,37 @@
       </c>
       <c r="H66" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="J66" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K66" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L66" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I66" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J66" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="K66" s="21" t="inlineStr">
+      <c r="M66" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N66" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L66" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M66" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N66" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5249,37 +5249,37 @@
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J67" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K67" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L67" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="I67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J67" s="21" t="inlineStr">
+      <c r="M67" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K67" s="21" t="inlineStr">
+      <c r="N67" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="L67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M67" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N67" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
         </is>
       </c>
     </row>
@@ -5321,37 +5321,37 @@
       </c>
       <c r="H68" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K68" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L68" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
         </is>
       </c>
-      <c r="I68" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J68" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K68" s="21" t="inlineStr">
+      <c r="M68" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N68" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L68" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M68" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="N68" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5403,27 +5403,27 @@
       </c>
       <c r="J69" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="K69" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K69" s="21" t="inlineStr">
+      <c r="M69" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="N69" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L69" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M69" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="N69" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
         </is>
       </c>
     </row>
@@ -5465,27 +5465,27 @@
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K70" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L70" s="21" t="inlineStr">
+        <is>
           <t>2:4</t>
-        </is>
-      </c>
-      <c r="I70" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="J70" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K70" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L70" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
       <c r="M70" s="21" t="inlineStr">
@@ -5537,37 +5537,37 @@
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J71" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K71" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L71" s="21" t="inlineStr">
+        <is>
           <t>0:5</t>
         </is>
       </c>
-      <c r="I71" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="J71" s="21" t="inlineStr">
+      <c r="M71" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="K71" s="21" t="inlineStr">
+      <c r="N71" s="21" t="inlineStr">
         <is>
           <t>0:4</t>
-        </is>
-      </c>
-      <c r="L71" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M71" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N71" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -5616,37 +5616,37 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J73" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="K73" s="21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="L73" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I73" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J73" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K73" s="21" t="inlineStr">
+      <c r="M73" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="N73" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L73" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M73" s="21" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="N73" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5693,32 @@
       </c>
       <c r="I74" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K74" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L74" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="J74" s="21" t="inlineStr">
+      <c r="M74" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="K74" s="21" t="inlineStr">
+      <c r="N74" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L74" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M74" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="N74" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -5760,37 +5760,37 @@
       </c>
       <c r="H75" s="21" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J75" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="K75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L75" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="I75" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="J75" s="21" t="inlineStr">
+      <c r="M75" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N75" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="K75" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="L75" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="M75" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="N75" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5832,32 @@
       </c>
       <c r="H76" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I76" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K76" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="L76" s="21" t="inlineStr">
+        <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="I76" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J76" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="K76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="M76" s="21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N76" s="21" t="inlineStr">
@@ -5909,32 +5909,32 @@
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J77" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K77" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="L77" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="J77" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K77" s="21" t="inlineStr">
+      <c r="M77" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="N77" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="L77" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M77" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="N77" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
     </row>
@@ -5976,32 +5976,32 @@
       </c>
       <c r="H78" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I78" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J78" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K78" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="L78" s="21" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="I78" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J78" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K78" s="21" t="inlineStr">
+      <c r="M78" s="21" t="inlineStr">
         <is>
           <t>0:0</t>
-        </is>
-      </c>
-      <c r="L78" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M78" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
         </is>
       </c>
       <c r="N78" s="21" t="inlineStr">
@@ -6055,37 +6055,37 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J80" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K80" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L80" s="21" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I80" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J80" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K80" s="21" t="inlineStr">
+      <c r="M80" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N80" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="L80" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M80" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="N80" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
     </row>
@@ -6137,27 +6137,27 @@
       </c>
       <c r="J81" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K81" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="K81" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L81" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="N81" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I82" s="21" t="inlineStr">
@@ -6209,27 +6209,27 @@
       </c>
       <c r="J82" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K82" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="L82" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M82" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N82" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="L82" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M82" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="N82" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -6271,32 +6271,32 @@
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J83" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K83" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
+        <is>
           <t>1:4</t>
         </is>
       </c>
-      <c r="I83" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="J83" s="21" t="inlineStr">
+      <c r="M83" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="K83" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L83" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M83" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N83" s="21" t="inlineStr">
@@ -6343,32 +6343,32 @@
       </c>
       <c r="H84" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I84" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
       <c r="J84" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K84" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="L84" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="K84" s="21" t="inlineStr">
+      <c r="M84" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="L84" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M84" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
         </is>
       </c>
       <c r="N84" s="21" t="inlineStr">
@@ -6415,37 +6415,37 @@
       </c>
       <c r="H85" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I85" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J85" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K85" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L85" s="21" t="inlineStr">
+        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="I85" s="21" t="inlineStr">
+      <c r="M85" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="N85" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="J85" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K85" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="L85" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M85" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="N85" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
     </row>
@@ -6531,37 +6531,37 @@
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Heiko Baust</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Egon Hejda</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Heiko Baust</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="M3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
         </is>
       </c>
     </row>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
           <t>Japan</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
     </row>
@@ -6908,27 +6908,27 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="M8" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
     </row>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
           <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="M10" s="21" t="inlineStr">
         <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
     </row>
@@ -7258,37 +7258,37 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
     </row>
@@ -7402,14 +7402,14 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="M14" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
     </row>
@@ -7546,37 +7546,37 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Neuseeland</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
-        <is>
-          <t>Neuseeland</t>
-        </is>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -7769,37 +7769,37 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
     </row>
@@ -7841,37 +7841,37 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -7913,37 +7913,37 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
     </row>
@@ -8129,37 +8129,37 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -8201,37 +8201,37 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
     </row>
@@ -8278,14 +8278,14 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="M27" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
     </row>
@@ -8362,27 +8362,27 @@
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
     </row>
@@ -8424,14 +8424,14 @@
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="J30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="M30" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N30" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
     </row>
@@ -8496,37 +8496,37 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
+      <c r="N31" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -8568,37 +8568,37 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="N32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
     </row>
@@ -8647,37 +8647,37 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
     </row>
@@ -8719,37 +8719,37 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
+      <c r="N35" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,32 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="M37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="N37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -641,14 +641,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Marco Schirmacher</t>
+          <t>Egon Hejda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>0</v>
@@ -715,14 +715,14 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Myles Davies</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -752,14 +752,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -789,14 +789,14 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -826,14 +826,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Egon Hejda</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -863,14 +863,14 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Heiko Baust</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -900,14 +900,14 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
@@ -937,14 +937,14 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Heiko Baust</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Myles Davies</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Marco Schirmacher</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -1048,14 +1048,14 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -1122,62 +1122,62 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Heiko Baust</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Marco Schirmacher</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Egon Hejda</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Heiko Baust</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
     </row>
@@ -1209,54 +1209,54 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
     </row>
@@ -1271,64 +1271,64 @@
           <t>2:1</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
     </row>
@@ -1355,52 +1355,52 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M5" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1561,62 +1561,62 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -1635,67 +1635,67 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
         </is>
       </c>
     </row>
@@ -1707,67 +1707,67 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -1804,42 +1804,42 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1856,62 +1856,62 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -1938,52 +1938,52 @@
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -2010,52 +2010,52 @@
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
     </row>
@@ -2074,67 +2074,67 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>4:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
         </is>
       </c>
     </row>
@@ -2146,67 +2146,67 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M18" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
         </is>
       </c>
     </row>
@@ -2223,62 +2223,62 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -2295,62 +2295,62 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -2377,52 +2377,52 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -2464,37 +2464,37 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2513,67 +2513,67 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+3)</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
         </is>
       </c>
     </row>
@@ -2585,67 +2585,67 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
         </is>
       </c>
     </row>
@@ -2662,62 +2662,62 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>3:3</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2734,62 +2734,62 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
       <c r="N27" s="21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -2816,47 +2816,47 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
       <c r="M28" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -2888,52 +2888,52 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
           <t>3:2</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -2952,67 +2952,67 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>7:0</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
+          <t>7:1</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>7:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="N31" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
         </is>
       </c>
     </row>
@@ -3024,67 +3024,67 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
         </is>
       </c>
     </row>
@@ -3111,52 +3111,52 @@
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="M33" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="N33" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K33" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="M33" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N33" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -3173,62 +3173,62 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
     </row>
@@ -3255,52 +3255,52 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
       <c r="L35" s="21" t="inlineStr">
         <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -3317,62 +3317,62 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J36" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
           <t>2:3</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J36" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N36" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -3391,67 +3391,67 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J38" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K38" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L38" s="21" t="inlineStr">
-        <is>
           <t>2:2</t>
         </is>
       </c>
-      <c r="M38" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N38" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
         </is>
       </c>
     </row>
@@ -3463,67 +3463,67 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G39" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H39" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J39" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L39" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="M39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N39" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L39" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
         </is>
       </c>
     </row>
@@ -3550,52 +3550,52 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="inlineStr">
         <is>
           <t>2:2</t>
-        </is>
-      </c>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K40" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="L40" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N40" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
     </row>
@@ -3612,62 +3612,62 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="J41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M41" s="21" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G41" s="21" t="inlineStr">
+      <c r="N41" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K41" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N41" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -3684,62 +3684,62 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="L42" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N42" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K42" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3766,47 +3766,47 @@
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="K43" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="L43" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="H43" s="21" t="inlineStr">
+      <c r="M43" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L43" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M43" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
         </is>
       </c>
       <c r="N43" s="21" t="inlineStr">
@@ -3835,62 +3835,62 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="H45" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J45" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K45" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="L45" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="F45" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="M45" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N45" s="21" t="inlineStr">
         <is>
           <t>3:2</t>
-        </is>
-      </c>
-      <c r="H45" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="J45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K45" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L45" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M45" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="N45" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -3907,62 +3907,62 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K46" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
         </is>
       </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="M46" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="N46" s="21" t="inlineStr">
         <is>
           <t>1:0</t>
-        </is>
-      </c>
-      <c r="H46" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I46" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J46" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K46" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M46" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N46" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3999,42 +3999,42 @@
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="J47" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K47" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L47" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M47" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N47" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="H47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="J47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="L47" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M47" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N47" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
         </is>
       </c>
     </row>
@@ -4051,62 +4051,62 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
+        <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="J48" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M48" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
+      <c r="N48" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="M48" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N48" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -4143,42 +4143,42 @@
       </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K49" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I49" s="21" t="inlineStr">
+      <c r="L49" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="M49" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J49" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K49" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="L49" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M49" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
       <c r="N49" s="21" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4215,42 +4215,42 @@
       </c>
       <c r="G50" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H50" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="H50" s="21" t="inlineStr">
+      <c r="J50" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="I50" s="21" t="inlineStr">
+      <c r="K50" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="J50" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K50" s="21" t="inlineStr">
+      <c r="L50" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M50" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="N50" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="L50" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="M50" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N50" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -4274,52 +4274,52 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
           <t>6:0</t>
         </is>
       </c>
-      <c r="D52" s="21" t="inlineStr">
+      <c r="E52" s="21" t="inlineStr">
         <is>
           <t>6:0</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="inlineStr">
+        <is>
+          <t>7:0</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="J52" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>6:0</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="inlineStr">
+      <c r="K52" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="H52" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="I52" s="21" t="inlineStr">
+      <c r="L52" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="J52" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>7:0</t>
         </is>
       </c>
       <c r="M52" s="21" t="inlineStr">
@@ -4346,62 +4346,62 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J53" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K53" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M53" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E53" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="F53" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G53" s="21" t="inlineStr">
+      <c r="N53" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H53" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J53" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="K53" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L53" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M53" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="N53" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -4428,52 +4428,52 @@
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G54" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="H54" s="21" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="J54" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I54" s="21" t="inlineStr">
+      <c r="K54" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="J54" s="21" t="inlineStr">
+      <c r="L54" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K54" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L54" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
       <c r="M54" s="21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="N54" s="21" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4490,62 +4490,62 @@
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="D55" s="21" t="inlineStr">
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H55" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J55" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="K55" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L55" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="N55" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="G55" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="H55" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J55" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K55" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L55" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M55" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="N55" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
         </is>
       </c>
     </row>
@@ -4562,62 +4562,62 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="D56" s="21" t="inlineStr">
+      <c r="E56" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H56" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J56" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K56" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="M56" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
-        </is>
-      </c>
-      <c r="G56" s="21" t="inlineStr">
+      <c r="N56" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H56" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I56" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="J56" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K56" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L56" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M56" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
-        </is>
-      </c>
-      <c r="N56" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -4634,57 +4634,57 @@
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H57" s="21" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="J57" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="K57" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="M57" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J57" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K57" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="L57" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
-        </is>
-      </c>
-      <c r="M57" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
         </is>
       </c>
       <c r="N57" s="21" t="inlineStr">
@@ -4713,57 +4713,57 @@
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H59" s="21" t="inlineStr">
+        <is>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="I59" s="21" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="J59" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K59" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="M59" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E59" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G59" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="H59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K59" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="L59" s="21" t="inlineStr">
-        <is>
-          <t>4:2</t>
-        </is>
-      </c>
-      <c r="M59" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
       <c r="N59" s="21" t="inlineStr">
@@ -4785,62 +4785,62 @@
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H60" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="J60" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K60" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L60" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M60" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="inlineStr">
+      <c r="N60" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="G60" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="H60" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I60" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J60" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="K60" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="L60" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="M60" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N60" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
     </row>
@@ -4857,62 +4857,62 @@
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="E61" s="21" t="inlineStr">
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="H61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H61" s="21" t="inlineStr">
+      <c r="I61" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="J61" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="I61" s="21" t="inlineStr">
+      <c r="K61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J61" s="21" t="inlineStr">
+      <c r="L61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="K61" s="21" t="inlineStr">
+      <c r="M61" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="L61" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M61" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
       <c r="N61" s="21" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -4939,52 +4939,52 @@
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H62" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I62" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="J62" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K62" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F62" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="inlineStr">
+      <c r="L62" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="H62" s="21" t="inlineStr">
+      <c r="M62" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I62" s="21" t="inlineStr">
+      <c r="N62" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
-        </is>
-      </c>
-      <c r="J62" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K62" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="L62" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M62" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N62" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5011,52 +5011,52 @@
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H63" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="J63" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K63" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="L63" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="M63" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
+      <c r="N63" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
-        </is>
-      </c>
-      <c r="H63" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I63" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J63" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K63" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="L63" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M63" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="N63" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -5098,37 +5098,37 @@
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="I64" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="J64" s="21" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="K64" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L64" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N64" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
-        </is>
-      </c>
-      <c r="K64" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="L64" s="21" t="inlineStr">
-        <is>
-          <t>5:2</t>
-        </is>
-      </c>
-      <c r="M64" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="N64" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -5162,42 +5162,42 @@
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F66" s="21" t="inlineStr">
+      <c r="H66" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I66" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="G66" s="21" t="inlineStr">
+      <c r="J66" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="H66" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I66" s="21" t="inlineStr">
+      <c r="K66" s="21" t="inlineStr">
         <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="J66" s="21" t="inlineStr">
+      <c r="L66" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="K66" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L66" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
         </is>
       </c>
       <c r="M66" s="21" t="inlineStr">
@@ -5224,24 +5224,24 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="D67" s="21" t="inlineStr">
+      <c r="E67" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="E67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
           <t>2:0</t>
@@ -5249,27 +5249,27 @@
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="J67" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="K67" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="J67" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K67" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="L67" s="21" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="M67" s="21" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="N67" s="21" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5296,57 +5296,57 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H68" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K68" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L68" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M68" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="E68" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F68" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G68" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="H68" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I68" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J68" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K68" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L68" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="M68" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
       <c r="N68" s="21" t="inlineStr">
@@ -5368,62 +5368,62 @@
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E69" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H69" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I69" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K69" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="M69" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="D69" s="21" t="inlineStr">
+      <c r="N69" s="21" t="inlineStr">
         <is>
           <t>0:1</t>
-        </is>
-      </c>
-      <c r="E69" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="F69" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="G69" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="H69" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I69" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J69" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="K69" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="L69" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="M69" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="N69" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5440,62 +5440,62 @@
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H70" s="21" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="K70" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="E70" s="21" t="inlineStr">
+      <c r="L70" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="F70" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="G70" s="21" t="inlineStr">
+      <c r="M70" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N70" s="21" t="inlineStr">
         <is>
           <t>2:3</t>
-        </is>
-      </c>
-      <c r="H70" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I70" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J70" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K70" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L70" s="21" t="inlineStr">
-        <is>
-          <t>2:4</t>
-        </is>
-      </c>
-      <c r="M70" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="N70" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
     </row>
@@ -5512,62 +5512,62 @@
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="D71" s="21" t="inlineStr">
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H71" s="21" t="inlineStr">
+        <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="J71" s="21" t="inlineStr">
         <is>
           <t>0:4</t>
         </is>
       </c>
-      <c r="E71" s="21" t="inlineStr">
+      <c r="K71" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="G71" s="21" t="inlineStr">
+      <c r="L71" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M71" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="N71" s="21" t="inlineStr">
         <is>
           <t>1:3</t>
-        </is>
-      </c>
-      <c r="H71" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I71" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="J71" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="K71" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="L71" s="21" t="inlineStr">
-        <is>
-          <t>0:5</t>
-        </is>
-      </c>
-      <c r="M71" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="N71" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
         </is>
       </c>
     </row>
@@ -5591,62 +5591,62 @@
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="D73" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="E73" s="21" t="inlineStr">
+      <c r="G73" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H73" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F73" s="21" t="inlineStr">
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="J73" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="K73" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L73" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="G73" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H73" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I73" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J73" s="21" t="inlineStr">
+      <c r="M73" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="K73" s="21" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="L73" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="M73" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
       <c r="N73" s="21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5663,62 +5663,62 @@
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="D74" s="21" t="inlineStr">
+      <c r="E74" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G74" s="21" t="inlineStr">
         <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F74" s="21" t="inlineStr">
+      <c r="H74" s="21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K74" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L74" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M74" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
         </is>
       </c>
-      <c r="G74" s="21" t="inlineStr">
+      <c r="N74" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="H74" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="I74" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J74" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K74" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L74" s="21" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="M74" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N74" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -5735,62 +5735,62 @@
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="inlineStr">
+        <is>
           <t>5:0</t>
         </is>
       </c>
-      <c r="D75" s="21" t="inlineStr">
+      <c r="H75" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="G75" s="21" t="inlineStr">
+      <c r="J75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="K75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="L75" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M75" s="21" t="inlineStr">
+        <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="N75" s="21" t="inlineStr">
         <is>
           <t>4:0</t>
-        </is>
-      </c>
-      <c r="H75" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="I75" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="J75" s="21" t="inlineStr">
-        <is>
-          <t>5:0</t>
-        </is>
-      </c>
-      <c r="K75" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="L75" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="M75" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N75" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
         </is>
       </c>
     </row>
@@ -5807,62 +5807,62 @@
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H76" s="21" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I76" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="J76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="K76" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L76" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M76" s="21" t="inlineStr">
+        <is>
           <t>4:0</t>
         </is>
       </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="E76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="G76" s="21" t="inlineStr">
+      <c r="N76" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="H76" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I76" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="J76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K76" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="L76" s="21" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="M76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N76" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -5879,62 +5879,62 @@
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="E77" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H77" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I77" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="J77" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="K77" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="L77" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M77" s="21" t="inlineStr">
+        <is>
           <t>1:3</t>
         </is>
       </c>
-      <c r="D77" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="E77" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="F77" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G77" s="21" t="inlineStr">
+      <c r="N77" s="21" t="inlineStr">
         <is>
           <t>1:2</t>
-        </is>
-      </c>
-      <c r="H77" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="I77" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="J77" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K77" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="L77" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M77" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="N77" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -5951,62 +5951,62 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="E78" s="21" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="F78" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H78" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I78" s="21" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="J78" s="21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="K78" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="L78" s="21" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="M78" s="21" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="E78" s="21" t="inlineStr">
-        <is>
-          <t>4:3</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="G78" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="H78" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I78" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="J78" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K78" s="21" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="L78" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="M78" s="21" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
       <c r="N78" s="21" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:0</t>
         </is>
       </c>
     </row>
@@ -6030,62 +6030,62 @@
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G80" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H80" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
+      <c r="J80" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K80" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L80" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="G80" s="21" t="inlineStr">
+      <c r="M80" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="H80" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I80" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J80" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K80" s="21" t="inlineStr">
+      <c r="N80" s="21" t="inlineStr">
         <is>
           <t>3:1</t>
-        </is>
-      </c>
-      <c r="L80" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="M80" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="N80" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
@@ -6112,52 +6112,52 @@
       </c>
       <c r="E81" s="21" t="inlineStr">
         <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I81" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="G81" s="21" t="inlineStr">
+      <c r="J81" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K81" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="M81" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N81" s="21" t="inlineStr">
         <is>
           <t>3:0</t>
-        </is>
-      </c>
-      <c r="H81" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="I81" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="J81" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K81" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="L81" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="M81" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="N81" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -6184,52 +6184,52 @@
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G82" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H82" s="21" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I82" s="21" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="J82" s="21" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="G82" s="21" t="inlineStr">
+      <c r="K82" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="L82" s="21" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="M82" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="N82" s="21" t="inlineStr">
         <is>
           <t>4:2</t>
-        </is>
-      </c>
-      <c r="H82" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I82" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="J82" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K82" s="21" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="L82" s="21" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="M82" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="N82" s="21" t="inlineStr">
-        <is>
-          <t>3:0</t>
         </is>
       </c>
     </row>
@@ -6256,47 +6256,47 @@
       </c>
       <c r="E83" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
       <c r="G83" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="J83" s="21" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="H83" s="21" t="inlineStr">
+      <c r="K83" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="M83" s="21" t="inlineStr">
         <is>
           <t>0:3</t>
-        </is>
-      </c>
-      <c r="I83" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="J83" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K83" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="L83" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="M83" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
         </is>
       </c>
       <c r="N83" s="21" t="inlineStr">
@@ -6318,57 +6318,57 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
           <t>0:5</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="J84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="K84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="L84" s="21" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="M84" s="21" t="inlineStr">
         <is>
           <t>0:5</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>0:4</t>
-        </is>
-      </c>
-      <c r="G84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="H84" s="21" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="J84" s="21" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K84" s="21" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="L84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
-        </is>
-      </c>
-      <c r="M84" s="21" t="inlineStr">
-        <is>
-          <t>0:3</t>
         </is>
       </c>
       <c r="N84" s="21" t="inlineStr">
@@ -6390,57 +6390,57 @@
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D85" s="21" t="inlineStr">
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="E85" s="21" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
+      <c r="H85" s="21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I85" s="21" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="J85" s="21" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G85" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="H85" s="21" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I85" s="21" t="inlineStr">
+      <c r="K85" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="J85" s="21" t="inlineStr">
+      <c r="L85" s="21" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="M85" s="21" t="inlineStr">
         <is>
           <t>2:1</t>
-        </is>
-      </c>
-      <c r="K85" s="21" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="L85" s="21" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="M85" s="21" t="inlineStr">
-        <is>
-          <t>1:0</t>
         </is>
       </c>
       <c r="N85" s="21" t="inlineStr">
@@ -6506,62 +6506,62 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
+          <t>Egon Hejda</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Heiko Baust</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Marco Schirmacher</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Egon Hejda</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Heiko Baust</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
     </row>
@@ -6585,62 +6585,62 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="M3" s="21" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="I3" s="21" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="K3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="M3" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
@@ -6836,27 +6836,27 @@
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -6883,52 +6883,52 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
     </row>
@@ -6960,42 +6960,42 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -7017,62 +7017,62 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
         </is>
       </c>
     </row>
@@ -7104,42 +7104,42 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -7233,57 +7233,57 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -7377,62 +7377,62 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
     </row>
@@ -7469,42 +7469,42 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
           <t>Kanada</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
     </row>
@@ -7531,52 +7531,52 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>Neuseeland</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>Neuseeland</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -7744,62 +7744,62 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -7816,62 +7816,62 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
     </row>
@@ -7888,57 +7888,57 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -7975,42 +7975,42 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K23" s="21" t="inlineStr">
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="M23" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -8032,57 +8032,57 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
+      <c r="M24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -8104,62 +8104,62 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="M25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
     </row>
@@ -8176,57 +8176,57 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -8263,42 +8263,42 @@
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -8327,62 +8327,62 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="M29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="N29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -8399,57 +8399,57 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K30" s="21" t="inlineStr">
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L30" s="21" t="inlineStr">
+      <c r="M30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M30" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -8471,57 +8471,57 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="M31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -8553,47 +8553,47 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -8632,52 +8632,52 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>
@@ -8694,57 +8694,57 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="N35" s="21" t="inlineStr">
@@ -8773,62 +8773,62 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="N37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
     </row>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>120</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>0</v>
@@ -678,17 +678,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Myles Davies</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>0</v>
@@ -715,17 +715,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Myles Davies</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>111</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -789,17 +789,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
@@ -826,17 +826,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>109</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>106</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>0</v>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>104</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
@@ -937,17 +937,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>102</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>102</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>97</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>85</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>0</v>
@@ -1127,29 +1127,29 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="K1" s="13" t="inlineStr">
         <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -1204,24 +1204,24 @@
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="H3" s="19" t="inlineStr">
@@ -1276,49 +1276,49 @@
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="M4" s="19" t="inlineStr">
@@ -1348,29 +1348,29 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -1420,49 +1420,49 @@
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -1494,47 +1494,47 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
@@ -1566,47 +1566,47 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -1643,49 +1643,49 @@
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -1717,47 +1717,47 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -1787,49 +1787,49 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M13" s="19" t="inlineStr">
@@ -1931,49 +1931,49 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -2003,49 +2003,49 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -2084,29 +2084,29 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
@@ -2117,14 +2117,14 @@
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
           <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
         </is>
       </c>
       <c r="M18" s="18" t="inlineStr">
@@ -2226,29 +2226,29 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -2300,29 +2300,29 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>5:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>5:1  (+2)</t>
-        </is>
-      </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
@@ -2333,14 +2333,14 @@
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M20" s="17" t="inlineStr">
@@ -2372,47 +2372,47 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+4)</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>0:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="M21" s="19" t="inlineStr">
@@ -2447,44 +2447,44 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
         </is>
       </c>
       <c r="M22" s="18" t="inlineStr">
@@ -2536,14 +2536,14 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2595,47 +2595,47 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -2665,29 +2665,29 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
@@ -2739,47 +2739,47 @@
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="H27" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -2811,47 +2811,47 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="M28" s="18" t="inlineStr">
@@ -2881,49 +2881,49 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -2962,47 +2962,47 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>7:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>7:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M31" s="19" t="inlineStr">
@@ -3032,29 +3032,29 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -3104,49 +3104,49 @@
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G33" s="18" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>3:2  (+3)</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J33" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
@@ -3178,47 +3178,47 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="M34" s="20" t="inlineStr">
@@ -3248,49 +3248,49 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
+      <c r="L35" s="19" t="inlineStr">
         <is>
           <t>0:7  (+2)</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M35" s="18" t="inlineStr">
@@ -3322,47 +3322,47 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M36" s="20" t="inlineStr">
@@ -3401,47 +3401,47 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>2:2  (+4)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J38" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L38" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="M38" s="20" t="inlineStr">
@@ -3471,49 +3471,49 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
@@ -3560,32 +3560,32 @@
       </c>
       <c r="G40" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="M40" s="20" t="inlineStr">
@@ -3615,29 +3615,29 @@
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
@@ -3687,49 +3687,49 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I42" s="20" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J42" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K42" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L42" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="M42" s="20" t="inlineStr">
@@ -3759,49 +3759,49 @@
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="L43" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="L43" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
         </is>
       </c>
       <c r="M43" s="17" t="inlineStr">
@@ -3840,29 +3840,29 @@
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="M45" s="20" t="inlineStr">
@@ -3910,49 +3910,49 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr">
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="inlineStr">
+        <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="K46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J46" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L46" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="M46" s="20" t="inlineStr">
@@ -3999,32 +3999,32 @@
       </c>
       <c r="G47" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="L47" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="M47" s="20" t="inlineStr">
@@ -4054,49 +4054,49 @@
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="inlineStr">
+        <is>
+          <t>2:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>2:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
@@ -4141,34 +4141,34 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K49" s="20" t="inlineStr">
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="L49" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="M49" s="20" t="inlineStr">
@@ -4200,47 +4200,47 @@
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E50" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
+      <c r="L50" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M50" s="19" t="inlineStr">
@@ -4279,47 +4279,47 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>7:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="G52" s="20" t="inlineStr">
-        <is>
-          <t>7:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H52" s="20" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="M52" s="20" t="inlineStr">
@@ -4351,47 +4351,47 @@
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H53" s="20" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
@@ -4428,24 +4428,24 @@
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="K54" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="M54" s="19" t="inlineStr">
@@ -4495,29 +4495,29 @@
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="M55" s="20" t="inlineStr">
@@ -4567,47 +4567,47 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L56" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="M56" s="20" t="inlineStr">
@@ -4639,47 +4639,47 @@
       </c>
       <c r="D57" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>2:4  (+2)</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr">
+      <c r="J57" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="J57" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K57" s="17" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
         <is>
           <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L57" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="M57" s="18" t="inlineStr">
@@ -4716,49 +4716,49 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>4:2  (+3)</t>
+        </is>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>4:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="J59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K59" s="19" t="inlineStr">
+      <c r="L59" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
         </is>
       </c>
       <c r="M59" s="17" t="inlineStr">
@@ -4788,29 +4788,29 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
         </is>
       </c>
       <c r="I60" s="19" t="inlineStr">
@@ -4865,26 +4865,26 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="H61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="K61" s="19" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L61" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M61" s="19" t="inlineStr">
@@ -4932,49 +4932,49 @@
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G62" s="20" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K62" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J62" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M62" s="18" t="inlineStr">
@@ -5006,47 +5006,47 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
       <c r="K63" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L63" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="M63" s="20" t="inlineStr">
@@ -5078,47 +5078,47 @@
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E64" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>5:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>5:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H64" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K64" s="19" t="inlineStr">
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L64" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="M64" s="19" t="inlineStr">
@@ -5160,44 +5160,44 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>4:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>4:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J66" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="M66" s="19" t="inlineStr">
@@ -5232,44 +5232,44 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H67" s="19" t="inlineStr">
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L67" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M67" s="18" t="inlineStr">
@@ -5299,31 +5299,31 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D68" s="19" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="H68" s="19" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L68" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M68" s="20" t="inlineStr">
@@ -5371,49 +5371,49 @@
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="E69" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="J69" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K69" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="J69" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L69" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M69" s="18" t="inlineStr">
@@ -5443,49 +5443,49 @@
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>2:4  (+0)</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>2:4  (+0)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="J70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="I70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="M70" s="20" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
+        <is>
           <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="I71" s="19" t="inlineStr">
@@ -5596,47 +5596,47 @@
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G73" s="20" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
       <c r="K73" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L73" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="M73" s="20" t="inlineStr">
@@ -5671,44 +5671,44 @@
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="inlineStr">
+      <c r="K74" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L74" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M74" s="19" t="inlineStr">
@@ -5738,49 +5738,49 @@
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
         <is>
           <t>5:0  (+4)</t>
         </is>
       </c>
-      <c r="E75" s="19" t="inlineStr">
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G75" s="19" t="inlineStr">
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K75" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L75" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="M75" s="19" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="inlineStr">
+        <is>
           <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
@@ -5884,29 +5884,29 @@
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>0:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
-        <is>
-          <t>0:0  (+4)</t>
-        </is>
-      </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
@@ -5917,14 +5917,14 @@
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="K77" s="20" t="inlineStr">
+      <c r="K77" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="M77" s="20" t="inlineStr">
@@ -5954,49 +5954,49 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>4:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>4:3  (+2)</t>
-        </is>
-      </c>
-      <c r="F78" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="H78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="H78" s="20" t="inlineStr">
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="I78" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J78" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K78" s="19" t="inlineStr">
+      <c r="L78" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="M78" s="18" t="inlineStr">
@@ -6038,26 +6038,26 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E80" s="19" t="inlineStr">
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G80" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G80" s="20" t="inlineStr">
+      <c r="H80" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H80" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="I80" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
@@ -6068,14 +6068,14 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="K80" s="18" t="inlineStr">
+      <c r="K80" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L80" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L80" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M80" s="18" t="inlineStr">
@@ -6105,49 +6105,49 @@
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D81" s="19" t="inlineStr">
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E81" s="18" t="inlineStr">
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J81" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K81" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="L81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J81" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L81" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="M81" s="19" t="inlineStr">
@@ -6179,47 +6179,47 @@
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J82" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G82" s="20" t="inlineStr">
+      <c r="L82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J82" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L82" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="M82" s="20" t="inlineStr">
@@ -6249,49 +6249,49 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G83" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E83" s="19" t="inlineStr">
+      <c r="H83" s="19" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="I83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F83" s="19" t="inlineStr">
+      <c r="J83" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G83" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="H83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J83" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="M83" s="19" t="inlineStr">
@@ -6321,49 +6321,49 @@
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D84" s="17" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="H84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F84" s="19" t="inlineStr">
+      <c r="I84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="K84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L84" s="19" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="G84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J84" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="K84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="L84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M84" s="19" t="inlineStr">
@@ -6393,31 +6393,31 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="E85" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="G85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G85" s="20" t="inlineStr">
+      <c r="H85" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H85" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
@@ -6428,14 +6428,14 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K85" s="17" t="inlineStr">
+      <c r="K85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M85" s="20" t="inlineStr">
@@ -6511,29 +6511,29 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
@@ -6546,12 +6546,12 @@
       </c>
       <c r="K1" s="13" t="inlineStr">
         <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -6595,42 +6595,42 @@
       </c>
       <c r="E3" s="21" t="inlineStr">
         <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="K3" s="21" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="M3" s="21" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t>Japan</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -6878,47 +6878,47 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -6955,22 +6955,22 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -7099,22 +7099,22 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -7238,47 +7238,47 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>Senegal</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -7387,24 +7387,24 @@
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
           <t>Kroatien</t>
@@ -7417,12 +7417,12 @@
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
           <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -7526,47 +7526,47 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>USA</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -7754,22 +7754,22 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -7826,24 +7826,24 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
@@ -7856,12 +7856,12 @@
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -7898,17 +7898,17 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -7970,22 +7970,22 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -8109,47 +8109,47 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>Senegal</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -8186,22 +8186,22 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -8258,22 +8258,22 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -8337,22 +8337,22 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -8409,22 +8409,22 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -8476,27 +8476,27 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -8548,47 +8548,47 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -8627,47 +8627,47 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -8699,27 +8699,27 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -8778,47 +8778,47 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>120</v>
@@ -654,7 +654,7 @@
         <v>84</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>113</v>
@@ -691,7 +691,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
@@ -715,20 +715,20 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Marco Schirmacher</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -789,20 +789,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -826,20 +826,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Marco Schirmacher</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>78</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -863,20 +863,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>81</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -900,20 +900,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -937,20 +937,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>81</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
@@ -974,20 +974,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1011,20 +1011,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>85</v>
@@ -1061,7 +1061,7 @@
         <v>81</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -1132,47 +1132,47 @@
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Marco Schirmacher</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
-        </is>
-      </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="N1" s="13" t="inlineStr">
@@ -1209,49 +1209,49 @@
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L3" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
         </is>
       </c>
       <c r="N3" s="18" t="inlineStr">
@@ -1283,47 +1283,47 @@
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M4" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N4" s="20" t="inlineStr">
@@ -1353,49 +1353,49 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -1425,49 +1425,49 @@
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
@@ -1499,47 +1499,47 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K7" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -1571,37 +1571,37 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -1653,44 +1653,44 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -1722,47 +1722,47 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -1792,49 +1792,49 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
@@ -1864,49 +1864,49 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="N13" s="19" t="inlineStr">
@@ -1936,49 +1936,49 @@
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -2013,44 +2013,44 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -2089,47 +2089,47 @@
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -2161,47 +2161,47 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
@@ -2241,39 +2241,39 @@
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M19" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -2305,37 +2305,37 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
           <t>5:1  (+2)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="L20" s="17" t="inlineStr">
@@ -2375,39 +2375,39 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>0:3  (+4)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="L21" s="19" t="inlineStr">
@@ -2447,49 +2447,49 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
+      <c r="M22" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -2531,44 +2531,44 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N24" s="18" t="inlineStr">
@@ -2600,47 +2600,47 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="N25" s="19" t="inlineStr">
@@ -2670,49 +2670,49 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -2744,47 +2744,47 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -2816,47 +2816,47 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+      <c r="L28" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="L28" s="19" t="inlineStr">
+      <c r="M28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -2886,49 +2886,49 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -2967,47 +2967,47 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
           <t>7:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="N31" s="19" t="inlineStr">
@@ -3042,44 +3042,44 @@
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>2:3  (+0)</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
@@ -3119,24 +3119,24 @@
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="H33" s="18" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
         <is>
           <t>3:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J33" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K33" s="19" t="inlineStr">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
@@ -3203,17 +3203,17 @@
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K34" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -3253,49 +3253,49 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="K35" s="18" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="M35" s="19" t="inlineStr">
         <is>
           <t>0:7  (+2)</t>
-        </is>
-      </c>
-      <c r="M35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -3327,47 +3327,47 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>2:3  (+0)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M36" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
@@ -3411,42 +3411,42 @@
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>2:2  (+4)</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="M38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J38" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -3476,49 +3476,49 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G39" s="20" t="inlineStr">
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K39" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M39" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N39" s="19" t="inlineStr">
@@ -3555,42 +3555,42 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="H40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K40" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M40" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -3620,49 +3620,49 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="G41" s="20" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="L41" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="I41" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="M41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M41" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -3697,44 +3697,44 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H42" s="18" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="I42" s="20" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J42" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K42" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M42" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
@@ -3766,47 +3766,47 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="17" t="inlineStr">
+      <c r="L43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="L43" s="18" t="inlineStr">
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="M43" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
         </is>
       </c>
       <c r="N43" s="19" t="inlineStr">
@@ -3845,47 +3845,47 @@
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J45" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K45" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M45" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -3920,44 +3920,44 @@
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G46" s="18" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J46" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M46" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -4004,32 +4004,32 @@
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -4064,44 +4064,44 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>2:3  (+2)</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="K48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M48" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="N48" s="20" t="inlineStr">
@@ -4138,42 +4138,42 @@
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K49" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
       <c r="L49" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N49" s="20" t="inlineStr">
@@ -4205,47 +4205,47 @@
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M50" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M50" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
@@ -4284,47 +4284,47 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="G52" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
       <c r="H52" s="20" t="inlineStr">
         <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
           <t>7:0  (+0)</t>
         </is>
       </c>
-      <c r="I52" s="20" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="J52" s="20" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -4361,42 +4361,42 @@
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M53" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
@@ -4428,47 +4428,47 @@
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="K54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L54" s="19" t="inlineStr">
+      <c r="M54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -4500,37 +4500,37 @@
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="L55" s="20" t="inlineStr">
@@ -4572,47 +4572,47 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M56" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M56" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="N56" s="18" t="inlineStr">
@@ -4642,49 +4642,49 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>2:4  (+2)</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr">
+      <c r="K57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="J57" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K57" s="18" t="inlineStr">
+      <c r="L57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="L57" s="17" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M57" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="N57" s="19" t="inlineStr">
@@ -4726,44 +4726,44 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J59" s="18" t="inlineStr">
         <is>
           <t>4:2  (+3)</t>
         </is>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K59" s="17" t="inlineStr">
+      <c r="L59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="L59" s="19" t="inlineStr">
+      <c r="M59" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
         </is>
       </c>
       <c r="N59" s="19" t="inlineStr">
@@ -4793,49 +4793,49 @@
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="L60" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="K60" s="18" t="inlineStr">
+      <c r="M60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="L60" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="M60" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="N60" s="17" t="inlineStr">
@@ -4865,39 +4865,39 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E61" s="19" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="H61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="K61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K61" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="L61" s="19" t="inlineStr">
@@ -4937,49 +4937,49 @@
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E62" s="19" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F62" s="18" t="inlineStr">
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H62" s="20" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="I62" s="18" t="inlineStr">
+      <c r="K62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="J62" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K62" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L62" s="20" t="inlineStr">
+      <c r="L62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="M62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="N62" s="18" t="inlineStr">
@@ -5009,49 +5009,49 @@
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H63" s="20" t="inlineStr">
+      <c r="J63" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="K63" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K63" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L63" s="19" t="inlineStr">
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M63" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N63" s="17" t="inlineStr">
@@ -5081,39 +5081,39 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
           <t>5:2  (+2)</t>
         </is>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K64" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="L64" s="19" t="inlineStr">
@@ -5160,49 +5160,49 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E66" s="19" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="I66" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K66" s="18" t="inlineStr">
         <is>
           <t>4:1  (+3)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="L66" s="19" t="inlineStr">
+      <c r="M66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="N66" s="19" t="inlineStr">
@@ -5232,49 +5232,49 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E67" s="19" t="inlineStr">
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H67" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I67" s="19" t="inlineStr">
+      <c r="M67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="N67" s="19" t="inlineStr">
@@ -5304,49 +5304,49 @@
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H68" s="19" t="inlineStr">
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="I68" s="20" t="inlineStr">
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K68" s="20" t="inlineStr">
+      <c r="L68" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="L68" s="20" t="inlineStr">
+      <c r="M68" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M68" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
@@ -5381,34 +5381,34 @@
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="I69" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="J69" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K69" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L69" s="18" t="inlineStr">
@@ -5448,49 +5448,49 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G70" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>2:4  (+0)</t>
         </is>
       </c>
-      <c r="I70" s="20" t="inlineStr">
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="J70" s="20" t="inlineStr">
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M70" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="M70" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -5527,42 +5527,42 @@
       </c>
       <c r="F71" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
+        <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J71" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K71" s="19" t="inlineStr">
+      <c r="L71" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="L71" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="M71" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
         </is>
       </c>
       <c r="N71" s="18" t="inlineStr">
@@ -5611,37 +5611,37 @@
       </c>
       <c r="G73" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="H73" s="20" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="K73" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M73" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
@@ -5671,39 +5671,39 @@
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E74" s="19" t="inlineStr">
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G74" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="I74" s="19" t="inlineStr">
+      <c r="K74" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K74" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
@@ -5743,34 +5743,34 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E75" s="19" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
         <is>
           <t>5:0  (+4)</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
+      <c r="I75" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="K75" s="19" t="inlineStr">
@@ -5822,42 +5822,42 @@
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="inlineStr">
+        <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G76" s="19" t="inlineStr">
+      <c r="I76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H76" s="19" t="inlineStr">
+      <c r="J76" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="I76" s="19" t="inlineStr">
+      <c r="K76" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K76" s="19" t="inlineStr">
+      <c r="L76" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M76" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -5887,49 +5887,49 @@
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
         <is>
           <t>0:0  (+4)</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="G77" s="20" t="inlineStr">
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="K77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
+      <c r="L77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="J77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L77" s="20" t="inlineStr">
+      <c r="M77" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
@@ -5961,47 +5961,47 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="G78" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I78" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J78" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L78" s="19" t="inlineStr">
+      <c r="L78" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="M78" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M78" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="N78" s="19" t="inlineStr">
@@ -6038,49 +6038,49 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F80" s="18" t="inlineStr">
+      <c r="G80" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="G80" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H80" s="20" t="inlineStr">
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J80" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I80" s="18" t="inlineStr">
+      <c r="K80" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="J80" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K80" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
       <c r="L80" s="18" t="inlineStr">
         <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="M80" s="18" t="inlineStr">
+        <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="M80" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
         </is>
       </c>
       <c r="N80" s="18" t="inlineStr">
@@ -6112,47 +6112,47 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G81" s="19" t="inlineStr">
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J81" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K81" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="N81" s="18" t="inlineStr">
@@ -6184,47 +6184,47 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G82" s="20" t="inlineStr">
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H82" s="20" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L82" s="20" t="inlineStr">
+        <is>
+          <t>4:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J82" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K82" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M82" s="20" t="inlineStr">
-        <is>
-          <t>4:2  (+0)</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -6254,49 +6254,49 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E83" s="19" t="inlineStr">
+      <c r="E83" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F83" s="19" t="inlineStr">
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G83" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="I83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J83" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
       </c>
-      <c r="I83" s="19" t="inlineStr">
+      <c r="K83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="J83" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K83" s="19" t="inlineStr">
+      <c r="L83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="L83" s="19" t="inlineStr">
+      <c r="M83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="M83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="N83" s="19" t="inlineStr">
@@ -6326,36 +6326,36 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="F84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F84" s="19" t="inlineStr">
+      <c r="G84" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="H84" s="19" t="inlineStr">
+      <c r="I84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I84" s="19" t="inlineStr">
+      <c r="J84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="J84" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="L84" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M84" s="19" t="inlineStr">
+        <is>
           <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="M84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="N84" s="19" t="inlineStr">
@@ -6398,49 +6398,49 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E85" s="18" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
+      <c r="I85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J85" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="H85" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
+      <c r="L85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N85" s="19" t="inlineStr">
@@ -6516,47 +6516,47 @@
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Marco Schirmacher</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Rony Burkart</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Rony Burkart</t>
-        </is>
-      </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Edgar Mayer</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="N1" s="13" t="inlineStr">
@@ -6580,65 +6580,65 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C3" s="21" t="inlineStr">
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="K3" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
+      <c r="N3" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -6652,65 +6652,65 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
@@ -6724,65 +6724,65 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
@@ -6796,65 +6796,65 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
@@ -6871,62 +6871,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
@@ -6943,62 +6943,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="M8" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -7015,62 +7015,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="M9" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
@@ -7087,62 +7087,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="M10" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -7159,62 +7159,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
@@ -7231,62 +7231,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -7303,62 +7303,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M13" s="21" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="N13" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -7375,62 +7375,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
@@ -7447,62 +7447,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="M15" s="21" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
@@ -7519,62 +7519,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>Neuseeland</t>
         </is>
@@ -7591,62 +7591,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="M17" s="21" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="N17" s="21" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -7663,62 +7663,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="M18" s="21" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -7754,47 +7754,47 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -7826,37 +7826,37 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -7898,32 +7898,32 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -8114,47 +8114,47 @@
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
           <t>Senegal</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -8186,37 +8186,37 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -8258,37 +8258,37 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -8337,47 +8337,47 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="M29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -8481,37 +8481,37 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -8558,42 +8558,42 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -8632,47 +8632,47 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
+      <c r="M34" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="N34" s="21" t="inlineStr">
@@ -8704,37 +8704,37 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -8783,47 +8783,47 @@
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="N37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>120</v>
@@ -654,10 +654,10 @@
         <v>84</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>204</v>
+        <v>259</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>113</v>
@@ -691,10 +691,10 @@
         <v>81</v>
       </c>
       <c r="F3" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <v>10</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
@@ -715,23 +715,23 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
@@ -752,23 +752,23 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
@@ -789,23 +789,23 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Marco Schirmacher</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
@@ -826,20 +826,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Marco Schirmacher</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -863,20 +863,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -900,20 +900,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -937,23 +937,23 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
@@ -974,20 +974,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>102</v>
@@ -1024,7 +1024,7 @@
         <v>75</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>85</v>
@@ -1061,7 +1061,7 @@
         <v>81</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -1132,42 +1132,42 @@
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -1209,44 +1209,44 @@
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L3" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
         </is>
       </c>
       <c r="M3" s="19" t="inlineStr">
@@ -1281,44 +1281,44 @@
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M4" s="17" t="inlineStr">
@@ -1353,44 +1353,44 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
       <c r="K5" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -1427,42 +1427,42 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -1497,44 +1497,44 @@
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -1658,34 +1658,34 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -1722,42 +1722,42 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -1792,44 +1792,44 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
@@ -1869,21 +1869,21 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -1941,39 +1941,39 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M14" s="19" t="inlineStr">
@@ -2008,44 +2008,44 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M15" s="18" t="inlineStr">
@@ -2094,37 +2094,37 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="M17" s="17" t="inlineStr">
@@ -2159,21 +2159,21 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
           <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
@@ -2231,21 +2231,21 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
@@ -2258,17 +2258,17 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -2310,37 +2310,37 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
           <t>5:1  (+2)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
         </is>
       </c>
       <c r="M20" s="17" t="inlineStr">
@@ -2380,39 +2380,39 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>0:3  (+4)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="M21" s="19" t="inlineStr">
@@ -2447,44 +2447,44 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="L22" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="M22" s="19" t="inlineStr">
@@ -2528,42 +2528,42 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M24" s="19" t="inlineStr">
@@ -2600,42 +2600,42 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -2670,44 +2670,44 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -2744,42 +2744,42 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -2816,37 +2816,37 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="K28" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L28" s="18" t="inlineStr">
@@ -2886,44 +2886,44 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -2967,42 +2967,42 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>7:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="M31" s="19" t="inlineStr">
@@ -3037,44 +3037,44 @@
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J32" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M32" s="18" t="inlineStr">
@@ -3109,44 +3109,44 @@
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>3:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>3:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
@@ -3183,42 +3183,42 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K34" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="M34" s="20" t="inlineStr">
@@ -3258,39 +3258,39 @@
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="K35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
         </is>
       </c>
       <c r="M35" s="19" t="inlineStr">
@@ -3327,42 +3327,42 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M36" s="20" t="inlineStr">
@@ -3406,42 +3406,42 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J38" s="17" t="inlineStr">
-        <is>
-          <t>2:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M38" s="20" t="inlineStr">
@@ -3476,44 +3476,44 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H39" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
       <c r="I39" s="19" t="inlineStr">
         <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
@@ -3550,42 +3550,42 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M40" s="19" t="inlineStr">
@@ -3620,44 +3620,44 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K41" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="M41" s="19" t="inlineStr">
@@ -3692,44 +3692,44 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J42" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K42" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="M42" s="20" t="inlineStr">
@@ -3771,32 +3771,32 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="L43" s="17" t="inlineStr">
@@ -3845,42 +3845,42 @@
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K45" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
         </is>
       </c>
       <c r="M45" s="20" t="inlineStr">
@@ -3917,42 +3917,42 @@
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="I46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I46" s="18" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J46" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="M46" s="20" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="K47" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="M47" s="20" t="inlineStr">
@@ -4059,44 +4059,44 @@
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G48" s="18" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>2:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L48" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>2:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
@@ -4143,32 +4143,32 @@
       </c>
       <c r="G49" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J49" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K49" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L49" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M49" s="20" t="inlineStr">
@@ -4205,42 +4205,42 @@
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K50" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L50" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="M50" s="19" t="inlineStr">
@@ -4284,32 +4284,32 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="G52" s="20" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="H52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
+          <t>7:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>7:0  (+0)</t>
         </is>
       </c>
       <c r="K52" s="20" t="inlineStr">
@@ -4356,42 +4356,42 @@
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H53" s="20" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="I53" s="20" t="inlineStr">
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
@@ -4428,42 +4428,42 @@
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M54" s="19" t="inlineStr">
@@ -4500,42 +4500,42 @@
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="G55" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="L55" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="M55" s="20" t="inlineStr">
@@ -4572,42 +4572,42 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K56" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L56" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L56" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="M56" s="20" t="inlineStr">
@@ -4642,34 +4642,34 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E57" s="19" t="inlineStr">
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F57" s="18" t="inlineStr">
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G57" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
         </is>
       </c>
       <c r="K57" s="18" t="inlineStr">
@@ -4731,24 +4731,24 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>4:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>4:2  (+3)</t>
         </is>
       </c>
       <c r="K59" s="17" t="inlineStr">
@@ -4795,42 +4795,42 @@
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="L60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L60" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="M60" s="18" t="inlineStr">
@@ -4870,39 +4870,39 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="J61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="K61" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L61" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M61" s="19" t="inlineStr">
@@ -4939,42 +4939,42 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="M62" s="20" t="inlineStr">
@@ -5011,42 +5011,42 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K63" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M63" s="19" t="inlineStr">
@@ -5083,42 +5083,42 @@
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>5:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>5:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="M64" s="19" t="inlineStr">
@@ -5160,21 +5160,21 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="G66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
@@ -5185,14 +5185,14 @@
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>4:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K66" s="18" t="inlineStr">
-        <is>
-          <t>4:1  (+3)</t>
         </is>
       </c>
       <c r="L66" s="19" t="inlineStr">
@@ -5237,39 +5237,39 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I67" s="19" t="inlineStr">
+      <c r="L67" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J67" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="M67" s="19" t="inlineStr">
@@ -5309,34 +5309,34 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F68" s="17" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H68" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
+      <c r="I68" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K68" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
@@ -5376,44 +5376,44 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="F69" s="18" t="inlineStr">
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="G69" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H69" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="K69" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L69" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="L69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
         </is>
       </c>
       <c r="M69" s="18" t="inlineStr">
@@ -5448,44 +5448,44 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E70" s="18" t="inlineStr">
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>2:4  (+0)</t>
+        </is>
+      </c>
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I70" s="20" t="inlineStr">
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
-        <is>
-          <t>2:4  (+0)</t>
-        </is>
-      </c>
-      <c r="K70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
         </is>
       </c>
       <c r="M70" s="20" t="inlineStr">
@@ -5520,44 +5520,44 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E71" s="19" t="inlineStr">
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G71" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K71" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="L71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="J71" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="K71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L71" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
         </is>
       </c>
       <c r="M71" s="19" t="inlineStr">
@@ -5601,42 +5601,42 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="G73" s="20" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M73" s="20" t="inlineStr">
@@ -5671,44 +5671,44 @@
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I74" s="20" t="inlineStr">
+      <c r="L74" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M74" s="19" t="inlineStr">
@@ -5743,44 +5743,44 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
         <is>
           <t>5:0  (+4)</t>
         </is>
       </c>
-      <c r="F75" s="19" t="inlineStr">
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
       <c r="I75" s="19" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="J75" s="19" t="inlineStr">
+      <c r="K75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="K75" s="19" t="inlineStr">
+      <c r="L75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M75" s="19" t="inlineStr">
@@ -5815,44 +5815,44 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E76" s="19" t="inlineStr">
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F76" s="19" t="inlineStr">
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K76" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L76" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K76" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L76" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="M76" s="19" t="inlineStr">
@@ -5887,44 +5887,44 @@
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F77" s="17" t="inlineStr">
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
         <is>
           <t>0:0  (+4)</t>
         </is>
       </c>
-      <c r="G77" s="18" t="inlineStr">
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L77" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H77" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J77" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M77" s="20" t="inlineStr">
@@ -5961,24 +5961,24 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="G78" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H78" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
@@ -5986,17 +5986,17 @@
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K78" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K78" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L78" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="M78" s="19" t="inlineStr">
@@ -6040,42 +6040,42 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G80" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H80" s="18" t="inlineStr">
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="K80" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="I80" s="20" t="inlineStr">
+      <c r="L80" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J80" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K80" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L80" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
         </is>
       </c>
       <c r="M80" s="18" t="inlineStr">
@@ -6110,44 +6110,44 @@
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I81" s="18" t="inlineStr">
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L81" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="M81" s="19" t="inlineStr">
@@ -6182,21 +6182,21 @@
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="G82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G82" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
@@ -6204,22 +6204,22 @@
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K82" s="20" t="inlineStr">
+        <is>
+          <t>4:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L82" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L82" s="20" t="inlineStr">
-        <is>
-          <t>4:2  (+0)</t>
         </is>
       </c>
       <c r="M82" s="20" t="inlineStr">
@@ -6254,34 +6254,34 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E83" s="20" t="inlineStr">
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F83" s="19" t="inlineStr">
+      <c r="G83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G83" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
       <c r="I83" s="19" t="inlineStr">
         <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="J83" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J83" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
         </is>
       </c>
       <c r="K83" s="19" t="inlineStr">
@@ -6326,24 +6326,24 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E84" s="17" t="inlineStr">
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="F84" s="19" t="inlineStr">
+      <c r="G84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G84" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="H84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
         </is>
       </c>
       <c r="I84" s="19" t="inlineStr">
@@ -6398,39 +6398,39 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E85" s="17" t="inlineStr">
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="F85" s="18" t="inlineStr">
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="G85" s="20" t="inlineStr">
+      <c r="I85" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J85" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="L85" s="20" t="inlineStr">
@@ -6516,42 +6516,42 @@
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -6593,52 +6593,52 @@
           <t>Kanada</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="M3" s="20" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -6739,17 +6739,17 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -6809,21 +6809,21 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
@@ -6831,22 +6831,22 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
           <t>Japan</t>
-        </is>
-      </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="K6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -6868,14 +6868,14 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
           <t>Norwegen</t>
         </is>
       </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Ecuador</t>
@@ -6883,50 +6883,50 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
@@ -6940,65 +6940,65 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -7012,60 +7012,60 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K9" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="L9" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="M9" s="20" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -7084,65 +7084,65 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -7156,65 +7156,65 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
@@ -7228,19 +7228,19 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
@@ -7248,45 +7248,45 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="K12" s="20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -7300,65 +7300,65 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M13" s="20" t="inlineStr">
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -7387,42 +7387,42 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -7444,65 +7444,65 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="K15" s="20" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="N15" s="20" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
@@ -7516,60 +7516,60 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
           <t>Ägypten</t>
         </is>
       </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -7588,65 +7588,65 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="M17" s="20" t="inlineStr">
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="N17" s="20" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -7663,62 +7663,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J18" s="20" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="M18" s="20" t="inlineStr">
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="N18" s="20" t="inlineStr">
+      <c r="N18" s="17" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -7739,65 +7739,65 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
@@ -7811,65 +7811,65 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
@@ -7883,65 +7883,65 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
@@ -7958,62 +7958,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K23" s="21" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -8030,62 +8030,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -8102,62 +8102,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="N25" s="21" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -8174,62 +8174,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -8246,62 +8246,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -8342,37 +8342,37 @@
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -8414,17 +8414,17 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -8481,37 +8481,37 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="K31" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -8563,27 +8563,27 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -8637,37 +8637,37 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -8704,37 +8704,37 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -8788,37 +8788,37 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -98,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>120</v>
@@ -654,7 +654,7 @@
         <v>84</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>10</v>
@@ -678,14 +678,14 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Myles Davies</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>81</v>
@@ -694,7 +694,7 @@
         <v>55</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
@@ -715,23 +715,23 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Myles Davies</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>81</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
@@ -863,23 +863,23 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>78</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
@@ -900,17 +900,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
         <v>242</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>55</v>
@@ -937,23 +937,23 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
@@ -974,20 +974,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Rony Burkart</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>102</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1011,20 +1011,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Rony Burkart</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>102</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -1127,14 +1127,14 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
           <t>Myles Davies</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
@@ -1152,27 +1152,27 @@
       </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
-        </is>
-      </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="N1" s="13" t="inlineStr">
@@ -1206,55 +1206,55 @@
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K3" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -1276,12 +1276,12 @@
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
@@ -1301,29 +1301,29 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K4" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L4" s="20" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="N4" s="20" t="inlineStr">
@@ -1350,14 +1350,14 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
@@ -1373,19 +1373,19 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -1420,57 +1420,57 @@
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="N6" s="19" t="inlineStr">
+      <c r="N6" s="18" t="inlineStr">
         <is>
           <t>4:2  (+2)</t>
         </is>
@@ -1487,59 +1487,59 @@
           <t>0:3</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -1638,59 +1638,59 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -1717,52 +1717,52 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -1782,62 +1782,62 @@
           <t>4:1</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
+      <c r="N12" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -1859,57 +1859,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="M13" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="N13" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -1931,54 +1931,54 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="L14" s="18" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -1998,27 +1998,27 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
@@ -2028,29 +2028,29 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M15" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -2084,52 +2084,52 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -2149,62 +2149,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="K18" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="N18" s="19" t="inlineStr">
+      <c r="N18" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -2221,49 +2221,49 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -2293,59 +2293,59 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>5:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>5:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
         </is>
       </c>
       <c r="N20" s="17" t="inlineStr">
@@ -2365,62 +2365,62 @@
           <t>0:3</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+4)</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>0:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="M21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="N21" s="19" t="inlineStr">
+      <c r="N21" s="18" t="inlineStr">
         <is>
           <t>2:3  (+2)</t>
         </is>
@@ -2437,59 +2437,59 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
       <c r="L22" s="18" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -2521,17 +2521,17 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -2541,37 +2541,37 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="N24" s="18" t="inlineStr">
+      <c r="N24" s="19" t="inlineStr">
         <is>
           <t>3:0  (+3)</t>
         </is>
@@ -2620,30 +2620,30 @@
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="N25" s="19" t="inlineStr">
+      <c r="N25" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -2660,27 +2660,27 @@
           <t>2:0</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -2762,29 +2762,29 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
         <is>
           <t>2:4  (+2)</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -2811,52 +2811,52 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
+      <c r="M28" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -2883,15 +2883,15 @@
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -2908,27 +2908,27 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -2955,62 +2955,62 @@
           <t>7:1</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>7:0  (+2)</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="K31" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="M31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
+      <c r="N31" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -3032,17 +3032,17 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -3052,37 +3052,37 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
           <t>2:3  (+0)</t>
         </is>
       </c>
-      <c r="J32" s="20" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="inlineStr">
+      <c r="L32" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="M32" s="18" t="inlineStr">
+      <c r="M32" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="N32" s="19" t="inlineStr">
+      <c r="N32" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -3104,16 +3104,16 @@
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
@@ -3129,32 +3129,32 @@
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I33" s="18" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>3:2  (+3)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="K33" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K33" s="17" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="L33" s="19" t="inlineStr">
+      <c r="M33" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="N33" s="19" t="inlineStr">
+      <c r="N33" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J34" s="20" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K34" s="20" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="L34" s="20" t="inlineStr">
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -3243,59 +3243,59 @@
           <t>0:2</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="J35" s="18" t="inlineStr">
+      <c r="J35" s="19" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="K35" s="18" t="inlineStr">
+      <c r="K35" s="19" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="L35" s="19" t="inlineStr">
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>0:7  (+2)</t>
+        </is>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="M35" s="19" t="inlineStr">
-        <is>
-          <t>0:7  (+2)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -3322,52 +3322,52 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
+      <c r="M36" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M36" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
@@ -3394,21 +3394,21 @@
           <t>2:2</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>0:0  (+3)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
@@ -3424,29 +3424,29 @@
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
         <is>
           <t>2:2  (+4)</t>
         </is>
       </c>
-      <c r="J38" s="20" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L38" s="18" t="inlineStr">
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M38" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -3466,21 +3466,21 @@
           <t>5:1</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
@@ -3491,37 +3491,37 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="J39" s="20" t="inlineStr">
+      <c r="K39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K39" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M39" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="M39" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="N39" s="19" t="inlineStr">
+      <c r="N39" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -3538,59 +3538,59 @@
           <t>5:1</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="K40" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="L40" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K40" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
+      <c r="M40" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -3610,17 +3610,17 @@
           <t>0:4</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -3630,37 +3630,37 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="J41" s="20" t="inlineStr">
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
+      <c r="L41" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="M41" s="19" t="inlineStr">
+      <c r="M41" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -3689,14 +3689,14 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
@@ -3712,29 +3712,29 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="J42" s="20" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L42" s="17" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M42" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
@@ -3754,62 +3754,62 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
+      <c r="F43" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="L43" s="19" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="17" t="inlineStr">
+      <c r="M43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="L43" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="M43" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="N43" s="19" t="inlineStr">
+      <c r="N43" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -3840,14 +3840,14 @@
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
@@ -3865,27 +3865,27 @@
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J45" s="20" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K45" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M45" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -3910,17 +3910,17 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+3)</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -3930,34 +3930,34 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr">
+      <c r="H46" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J46" s="20" t="inlineStr">
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L46" s="18" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M46" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -4009,27 +4009,27 @@
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -4049,17 +4049,17 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -4079,29 +4079,29 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
         <is>
           <t>2:3  (+2)</t>
         </is>
       </c>
-      <c r="J48" s="19" t="inlineStr">
+      <c r="K48" s="18" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
       <c r="L48" s="18" t="inlineStr">
         <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M48" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
         </is>
       </c>
       <c r="N48" s="20" t="inlineStr">
@@ -4151,29 +4151,29 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="J49" s="20" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K49" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L49" s="17" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
         </is>
       </c>
       <c r="N49" s="20" t="inlineStr">
@@ -4193,62 +4193,62 @@
           <t>1:5</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E50" s="19" t="inlineStr">
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="J50" s="19" t="inlineStr">
+      <c r="K50" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L50" s="19" t="inlineStr">
+      <c r="L50" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="M50" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="N50" s="19" t="inlineStr">
+      <c r="N50" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
@@ -4279,52 +4279,52 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G52" s="20" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="H52" s="20" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>7:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>7:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
+      <c r="M52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -4351,52 +4351,52 @@
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
+      <c r="M53" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="M53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
@@ -4416,59 +4416,59 @@
           <t>4:0</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E54" s="19" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="J54" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L54" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -4495,52 +4495,52 @@
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M55" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="N55" s="20" t="inlineStr">
@@ -4567,55 +4567,55 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L56" s="18" t="inlineStr">
+      <c r="M56" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="M56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="N56" s="18" t="inlineStr">
+      <c r="N56" s="19" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
@@ -4632,62 +4632,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F57" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="I57" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
+        <is>
           <t>2:4  (+2)</t>
         </is>
       </c>
-      <c r="J57" s="18" t="inlineStr">
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="K57" s="18" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="M57" s="19" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="L57" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="M57" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="N57" s="19" t="inlineStr">
+      <c r="N57" s="18" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
@@ -4711,62 +4711,62 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F59" s="18" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I59" s="18" t="inlineStr">
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>4:2  (+3)</t>
         </is>
       </c>
-      <c r="J59" s="17" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="K59" s="17" t="inlineStr">
+      <c r="L59" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="L59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M59" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N59" s="19" t="inlineStr">
+      <c r="N59" s="18" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
@@ -4783,57 +4783,57 @@
           <t>1:4</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C60" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="J60" s="18" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="K60" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L60" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="M60" s="18" t="inlineStr">
+      <c r="M60" s="19" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
@@ -4855,7 +4855,7 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -4880,34 +4880,34 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="J61" s="17" t="inlineStr">
+      <c r="K61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="K61" s="19" t="inlineStr">
+      <c r="L61" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="L61" s="19" t="inlineStr">
+      <c r="M61" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M61" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="N61" s="17" t="inlineStr">
@@ -4927,62 +4927,62 @@
           <t>3:2</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E62" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G62" s="18" t="inlineStr">
+      <c r="G62" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="H62" s="19" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="I62" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="J62" s="18" t="inlineStr">
+      <c r="K62" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="K62" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="M62" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="M62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="N62" s="18" t="inlineStr">
+      <c r="N62" s="19" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
@@ -4999,59 +4999,59 @@
           <t>1:4</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="L63" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M63" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L63" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M63" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
         </is>
       </c>
       <c r="N63" s="17" t="inlineStr">
@@ -5071,27 +5071,27 @@
           <t>5:0</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E64" s="19" t="inlineStr">
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F64" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -5101,32 +5101,32 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr">
         <is>
           <t>5:2  (+2)</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="K64" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K64" s="19" t="inlineStr">
+      <c r="L64" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="L64" s="20" t="inlineStr">
+      <c r="M64" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="M64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N64" s="19" t="inlineStr">
+      <c r="N64" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
@@ -5150,62 +5150,62 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E66" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="J66" s="18" t="inlineStr">
         <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
+        <is>
           <t>4:1  (+3)</t>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="L66" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M66" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="L66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N66" s="19" t="inlineStr">
+      <c r="N66" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -5222,62 +5222,62 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F67" s="18" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H67" s="19" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="I67" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="J67" s="19" t="inlineStr">
+      <c r="K67" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="K67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L67" s="19" t="inlineStr">
+      <c r="L67" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M67" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="M67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N67" s="19" t="inlineStr">
+      <c r="N67" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -5294,27 +5294,27 @@
           <t>2:0</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="E68" s="19" t="inlineStr">
+      <c r="F68" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -5324,29 +5324,29 @@
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="I68" s="19" t="inlineStr">
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J68" s="18" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="J68" s="20" t="inlineStr">
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K68" s="20" t="inlineStr">
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M68" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L68" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M68" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
@@ -5371,54 +5371,54 @@
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="G69" s="19" t="inlineStr">
+      <c r="G69" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="H69" s="19" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="J69" s="17" t="inlineStr">
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="K69" s="18" t="inlineStr">
+      <c r="L69" s="19" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="L69" s="20" t="inlineStr">
+      <c r="M69" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -5445,52 +5445,52 @@
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J70" s="20" t="inlineStr">
+        <is>
+          <t>2:4  (+0)</t>
+        </is>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="M70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
-        <is>
-          <t>2:4  (+0)</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K70" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -5517,55 +5517,55 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="F71" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
+      <c r="G71" s="18" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="H71" s="19" t="inlineStr">
+      <c r="H71" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I71" s="19" t="inlineStr">
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="J71" s="19" t="inlineStr">
+      <c r="K71" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="K71" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="L71" s="19" t="inlineStr">
+      <c r="L71" s="18" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="M71" s="19" t="inlineStr">
+      <c r="M71" s="18" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="N71" s="18" t="inlineStr">
+      <c r="N71" s="19" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -5621,27 +5621,27 @@
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="K73" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M73" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M73" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
@@ -5668,52 +5668,52 @@
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E74" s="19" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H74" s="19" t="inlineStr">
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="K74" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
+      <c r="L74" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="L74" s="20" t="inlineStr">
+      <c r="M74" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
@@ -5733,62 +5733,62 @@
           <t>5:0</t>
         </is>
       </c>
-      <c r="C75" s="19" t="inlineStr">
+      <c r="C75" s="18" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="D75" s="19" t="inlineStr">
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E75" s="19" t="inlineStr">
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
+      <c r="I75" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="J75" s="19" t="inlineStr">
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="K75" s="19" t="inlineStr">
+      <c r="L75" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="L75" s="19" t="inlineStr">
+      <c r="M75" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="M75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N75" s="19" t="inlineStr">
+      <c r="N75" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
@@ -5805,57 +5805,57 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="F76" s="19" t="inlineStr">
+      <c r="F76" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G76" s="19" t="inlineStr">
+      <c r="G76" s="18" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H76" s="19" t="inlineStr">
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I76" s="19" t="inlineStr">
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J76" s="18" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="J76" s="19" t="inlineStr">
+      <c r="K76" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="K76" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L76" s="19" t="inlineStr">
+      <c r="L76" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="M76" s="19" t="inlineStr">
+      <c r="M76" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -5877,59 +5877,59 @@
           <t>0:0</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>0:0  (+4)</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="K77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M77" s="19" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G77" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H77" s="17" t="inlineStr">
-        <is>
-          <t>0:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M77" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
@@ -5949,21 +5949,21 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C78" s="18" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D78" s="19" t="inlineStr">
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
         <is>
           <t>4:3  (+2)</t>
         </is>
       </c>
-      <c r="E78" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
@@ -5979,32 +5979,32 @@
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="I78" s="20" t="inlineStr">
+      <c r="I78" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="J78" s="20" t="inlineStr">
+      <c r="K78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K78" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L78" s="20" t="inlineStr">
+      <c r="L78" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="M78" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N78" s="19" t="inlineStr">
+      <c r="N78" s="18" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
@@ -6028,27 +6028,27 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C80" s="18" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D80" s="19" t="inlineStr">
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E80" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F80" s="19" t="inlineStr">
+      <c r="F80" s="18" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G80" s="18" t="inlineStr">
+      <c r="G80" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -6058,32 +6058,32 @@
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I80" s="20" t="inlineStr">
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J80" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J80" s="18" t="inlineStr">
+      <c r="K80" s="19" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="K80" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L80" s="20" t="inlineStr">
+      <c r="L80" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="M80" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="M80" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="N80" s="18" t="inlineStr">
+      <c r="N80" s="19" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -6100,62 +6100,62 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C81" s="19" t="inlineStr">
+      <c r="C81" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="F81" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G81" s="19" t="inlineStr">
+      <c r="G81" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H81" s="19" t="inlineStr">
+      <c r="H81" s="18" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="I81" s="19" t="inlineStr">
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="J81" s="19" t="inlineStr">
+      <c r="K81" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
       <c r="L81" s="18" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M81" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="M81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N81" s="18" t="inlineStr">
+      <c r="N81" s="19" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -6177,16 +6177,16 @@
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr">
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E82" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
@@ -6204,27 +6204,27 @@
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
+          <t>4:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J82" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J82" s="20" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K82" s="20" t="inlineStr">
-        <is>
-          <t>4:2  (+0)</t>
-        </is>
-      </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M82" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -6244,62 +6244,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C83" s="19" t="inlineStr">
+      <c r="C83" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E83" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G83" s="19" t="inlineStr">
+      <c r="G83" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="H83" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I83" s="19" t="inlineStr">
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
       </c>
-      <c r="J83" s="19" t="inlineStr">
+      <c r="K83" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="K83" s="19" t="inlineStr">
+      <c r="L83" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="L83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="N83" s="19" t="inlineStr">
+      <c r="N83" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -6316,62 +6316,62 @@
           <t>0:2</t>
         </is>
       </c>
-      <c r="C84" s="19" t="inlineStr">
+      <c r="C84" s="18" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D84" s="19" t="inlineStr">
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="G84" s="19" t="inlineStr">
+      <c r="G84" s="18" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="H84" s="19" t="inlineStr">
+      <c r="H84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I84" s="19" t="inlineStr">
+      <c r="I84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="J84" s="19" t="inlineStr">
+      <c r="J84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="K84" s="19" t="inlineStr">
+      <c r="K84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="L84" s="19" t="inlineStr">
+      <c r="L84" s="18" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="M84" s="18" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="M84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="N84" s="19" t="inlineStr">
+      <c r="N84" s="18" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
@@ -6393,57 +6393,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D85" s="19" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H85" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="J85" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
+      <c r="L85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="H85" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K85" s="20" t="inlineStr">
+      <c r="M85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="L85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="N85" s="19" t="inlineStr">
+      <c r="N85" s="18" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
           <t>Myles Davies</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
@@ -6536,27 +6536,27 @@
       </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
           <t>Christian Sandritter</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
-        </is>
-      </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
           <t>Rony Burkart</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="N1" s="13" t="inlineStr">
@@ -6588,54 +6588,54 @@
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="M3" s="20" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
         </is>
       </c>
       <c r="N3" s="17" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -6804,16 +6804,16 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
@@ -6846,12 +6846,12 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
           <t>Japan</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -6878,14 +6878,14 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
@@ -6901,29 +6901,29 @@
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="N7" s="17" t="inlineStr">
@@ -7020,16 +7020,16 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
@@ -7060,14 +7060,14 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -7236,54 +7236,54 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
         </is>
       </c>
       <c r="N12" s="17" t="inlineStr">
@@ -7375,59 +7375,59 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -7479,17 +7479,17 @@
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>Kanada</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr">
@@ -7524,16 +7524,16 @@
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
           <t>USA</t>
@@ -7551,27 +7551,27 @@
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
           <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Kolumbien</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Kolumbien</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7772,19 +7772,19 @@
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -7811,62 +7811,62 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="M21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -7883,14 +7883,14 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
@@ -7918,12 +7918,12 @@
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -8109,14 +8109,14 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
@@ -8149,12 +8149,12 @@
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -8357,17 +8357,17 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="K29" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -8548,52 +8548,52 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -8627,52 +8627,52 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
       <c r="L34" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="N34" s="21" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
+        <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -8778,52 +8778,52 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="N37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -98,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>120</v>
@@ -657,7 +657,7 @@
         <v>65</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -678,14 +678,14 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Myles Davies</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>81</v>
@@ -694,7 +694,7 @@
         <v>55</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
@@ -715,14 +715,14 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Myles Davies</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>81</v>
@@ -731,7 +731,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
@@ -752,23 +752,23 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>55</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
@@ -789,23 +789,23 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Marco Schirmacher</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>50</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
@@ -826,23 +826,23 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
@@ -863,23 +863,23 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
@@ -900,23 +900,23 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>55</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
@@ -937,23 +937,23 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Marco Schirmacher</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>102</v>
@@ -990,7 +990,7 @@
         <v>60</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>102</v>
@@ -1027,7 +1027,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>85</v>
@@ -1064,7 +1064,7 @@
         <v>55</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
@@ -1127,42 +1127,42 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="L1" s="13" t="inlineStr">
@@ -1206,55 +1206,55 @@
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="M3" s="18" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -1276,44 +1276,44 @@
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr">
@@ -1350,42 +1350,42 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
           <t>3:2  (+0)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K5" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -1420,42 +1420,42 @@
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -1465,12 +1465,12 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="N6" s="19" t="inlineStr">
         <is>
           <t>4:2  (+2)</t>
         </is>
@@ -1487,52 +1487,52 @@
           <t>0:3</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -1566,42 +1566,42 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -1638,49 +1638,49 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -1782,62 +1782,62 @@
           <t>4:1</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="N12" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -1859,57 +1859,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M13" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="N13" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -1931,52 +1931,52 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="K14" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
@@ -1998,52 +1998,52 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr">
@@ -2149,62 +2149,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="L18" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="N18" s="18" t="inlineStr">
+      <c r="N18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -2221,49 +2221,49 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>0:1  (+4)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -2293,57 +2293,57 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>5:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>5:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
+      <c r="M20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -2365,62 +2365,62 @@
           <t>0:3</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+4)</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="L21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="M21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>0:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
+      <c r="N21" s="19" t="inlineStr">
         <is>
           <t>2:3  (+2)</t>
         </is>
@@ -2437,57 +2437,57 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -2521,57 +2521,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="L24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N24" s="19" t="inlineStr">
+      <c r="N24" s="18" t="inlineStr">
         <is>
           <t>3:0  (+3)</t>
         </is>
@@ -2605,45 +2605,45 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
+      <c r="N25" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -2660,49 +2660,49 @@
           <t>2:0</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -2744,37 +2744,37 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -2811,50 +2811,50 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
+      <c r="L28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -2883,37 +2883,37 @@
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -2955,62 +2955,62 @@
           <t>7:1</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>7:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>7:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="K31" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="18" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M31" s="18" t="inlineStr">
+      <c r="M31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="N31" s="18" t="inlineStr">
+      <c r="N31" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -3032,57 +3032,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="L32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J32" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="M32" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="N32" s="18" t="inlineStr">
+      <c r="N32" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -3104,57 +3104,57 @@
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>3:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K33" s="18" t="inlineStr">
+      <c r="M33" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M33" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N33" s="18" t="inlineStr">
+      <c r="N33" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
@@ -3183,37 +3183,37 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K34" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="L34" s="20" t="inlineStr">
@@ -3243,57 +3243,57 @@
           <t>0:2</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
+      <c r="L35" s="19" t="inlineStr">
         <is>
           <t>0:7  (+2)</t>
         </is>
       </c>
-      <c r="M35" s="18" t="inlineStr">
+      <c r="M35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -3322,42 +3322,42 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
         <is>
           <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="L36" s="20" t="inlineStr">
@@ -3394,57 +3394,57 @@
           <t>2:2</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>0:0  (+3)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J38" s="17" t="inlineStr">
-        <is>
-          <t>2:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K38" s="20" t="inlineStr">
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M38" s="19" t="inlineStr">
+      <c r="M38" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -3466,62 +3466,62 @@
           <t>5:1</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="M39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J39" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M39" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N39" s="18" t="inlineStr">
+      <c r="N39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -3538,52 +3538,52 @@
           <t>5:1</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J40" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L40" s="18" t="inlineStr">
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -3610,57 +3610,57 @@
           <t>0:4</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G41" s="18" t="inlineStr">
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="H41" s="18" t="inlineStr">
+      <c r="L41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J41" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K41" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L41" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="M41" s="18" t="inlineStr">
+      <c r="M41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -3689,37 +3689,37 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="J42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
         </is>
       </c>
       <c r="K42" s="20" t="inlineStr">
@@ -3754,62 +3754,62 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="L43" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="J43" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L43" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="M43" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="N43" s="18" t="inlineStr">
+      <c r="N43" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -3840,37 +3840,37 @@
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="K45" s="20" t="inlineStr">
@@ -3910,52 +3910,52 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
         <is>
           <t>0:0  (+3)</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H46" s="19" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J46" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K46" s="20" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M46" s="19" t="inlineStr">
+      <c r="M46" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -3994,32 +3994,32 @@
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G47" s="20" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="L47" s="20" t="inlineStr">
@@ -4049,57 +4049,57 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E48" s="19" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>2:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="H48" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>2:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="inlineStr">
+      <c r="L48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="L48" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="inlineStr">
+      <c r="M48" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -4136,29 +4136,29 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="G49" s="20" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J49" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="K49" s="20" t="inlineStr">
@@ -4193,62 +4193,62 @@
           <t>1:5</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L50" s="18" t="inlineStr">
+      <c r="L50" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="M50" s="18" t="inlineStr">
+      <c r="M50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="N50" s="18" t="inlineStr">
+      <c r="N50" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
@@ -4279,42 +4279,42 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>7:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="G52" s="20" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>7:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="L52" s="20" t="inlineStr">
@@ -4351,42 +4351,42 @@
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="L53" s="20" t="inlineStr">
@@ -4416,57 +4416,57 @@
           <t>4:0</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="18" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H54" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J54" s="18" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="K54" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L54" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M54" s="18" t="inlineStr">
+      <c r="M54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
@@ -4495,42 +4495,42 @@
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="L55" s="20" t="inlineStr">
@@ -4567,55 +4567,55 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="M56" s="19" t="inlineStr">
+      <c r="M56" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="N56" s="19" t="inlineStr">
+      <c r="N56" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
@@ -4632,62 +4632,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="M57" s="18" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J57" s="18" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="K57" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="L57" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M57" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="N57" s="18" t="inlineStr">
+      <c r="N57" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
@@ -4711,62 +4711,62 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>4:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
+      <c r="J59" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M59" s="17" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
-        <is>
-          <t>4:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L59" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="N59" s="18" t="inlineStr">
+      <c r="N59" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
@@ -4783,57 +4783,57 @@
           <t>1:4</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G60" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J60" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K60" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L60" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="M60" s="19" t="inlineStr">
+      <c r="M60" s="18" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
@@ -4855,7 +4855,7 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -4865,47 +4865,47 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
+      <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K61" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L61" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M61" s="18" t="inlineStr">
+      <c r="M61" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
@@ -4927,62 +4927,62 @@
           <t>3:2</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="E62" s="19" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
+      <c r="J62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="H62" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I62" s="19" t="inlineStr">
+      <c r="K62" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="J62" s="20" t="inlineStr">
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="K62" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
       <c r="M62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="N62" s="19" t="inlineStr">
+      <c r="N62" s="18" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
@@ -4999,57 +4999,57 @@
           <t>1:4</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E63" s="18" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
+      <c r="K63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K63" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L63" s="18" t="inlineStr">
+      <c r="L63" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="M63" s="18" t="inlineStr">
+      <c r="M63" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
@@ -5071,62 +5071,62 @@
           <t>5:0</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D64" s="18" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>5:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F64" s="18" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G64" s="18" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H64" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="J64" s="18" t="inlineStr">
-        <is>
-          <t>5:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K64" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L64" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="M64" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="N64" s="18" t="inlineStr">
+      <c r="N64" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
@@ -5150,62 +5150,62 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>4:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="M66" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="J66" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L66" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M66" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N66" s="18" t="inlineStr">
+      <c r="N66" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -5222,62 +5222,62 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="K67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="I67" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K67" s="18" t="inlineStr">
+      <c r="L67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="L67" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M67" s="18" t="inlineStr">
+      <c r="M67" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="N67" s="18" t="inlineStr">
+      <c r="N67" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
@@ -5294,49 +5294,49 @@
           <t>2:0</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K68" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K68" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="L68" s="20" t="inlineStr">
@@ -5371,47 +5371,47 @@
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="H69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H69" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I69" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="L69" s="19" t="inlineStr">
+      <c r="L69" s="18" t="inlineStr">
         <is>
           <t>0:1  (+3)</t>
         </is>
@@ -5445,37 +5445,37 @@
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>2:4  (+0)</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
-        <is>
-          <t>2:4  (+0)</t>
         </is>
       </c>
       <c r="K70" s="20" t="inlineStr">
@@ -5517,55 +5517,55 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F71" s="18" t="inlineStr">
+      <c r="J71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G71" s="18" t="inlineStr">
+      <c r="K71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="H71" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="J71" s="18" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="K71" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L71" s="18" t="inlineStr">
+      <c r="L71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="M71" s="18" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="N71" s="19" t="inlineStr">
+      <c r="N71" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -5601,37 +5601,37 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="G73" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="L73" s="20" t="inlineStr">
@@ -5668,45 +5668,45 @@
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E74" s="19" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G74" s="18" t="inlineStr">
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="K74" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L74" s="18" t="inlineStr">
+      <c r="L74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -5733,62 +5733,62 @@
           <t>5:0</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
+      <c r="K75" s="17" t="inlineStr">
         <is>
           <t>5:0  (+4)</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H75" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
+      <c r="L75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K75" s="18" t="inlineStr">
+      <c r="M75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="L75" s="18" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M75" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N75" s="18" t="inlineStr">
+      <c r="N75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
@@ -5805,57 +5805,57 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C76" s="19" t="inlineStr">
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="H76" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F76" s="18" t="inlineStr">
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K76" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H76" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I76" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J76" s="18" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K76" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L76" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M76" s="18" t="inlineStr">
+      <c r="M76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
@@ -5877,57 +5877,57 @@
           <t>0:0</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C77" s="18" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D77" s="19" t="inlineStr">
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>0:0  (+4)</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="H77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G77" s="20" t="inlineStr">
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K77" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
-        <is>
-          <t>0:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J77" s="19" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="M77" s="19" t="inlineStr">
+      <c r="M77" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -5949,62 +5949,62 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C78" s="19" t="inlineStr">
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>4:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>4:3  (+2)</t>
-        </is>
-      </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H78" s="20" t="inlineStr">
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="I78" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K78" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L78" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="N78" s="18" t="inlineStr">
+      <c r="N78" s="19" t="inlineStr">
         <is>
           <t>3:2  (+2)</t>
         </is>
@@ -6028,62 +6028,62 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C80" s="19" t="inlineStr">
+      <c r="C80" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G80" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="E80" s="18" t="inlineStr">
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="I80" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G80" s="19" t="inlineStr">
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="K80" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="H80" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I80" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J80" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K80" s="19" t="inlineStr">
+      <c r="L80" s="18" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="L80" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
       <c r="M80" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="N80" s="19" t="inlineStr">
+      <c r="N80" s="18" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -6100,62 +6100,62 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C81" s="18" t="inlineStr">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
         <is>
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
+      <c r="H81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="M81" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F81" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G81" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H81" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I81" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J81" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K81" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L81" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M81" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="N81" s="19" t="inlineStr">
+      <c r="N81" s="18" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -6177,39 +6177,39 @@
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="D82" s="19" t="inlineStr">
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="E82" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>4:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G82" s="20" t="inlineStr">
+      <c r="J82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I82" s="20" t="inlineStr">
-        <is>
-          <t>4:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="K82" s="20" t="inlineStr">
@@ -6244,62 +6244,62 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="E83" s="18" t="inlineStr">
+      <c r="H83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F83" s="20" t="inlineStr">
+      <c r="I83" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G83" s="18" t="inlineStr">
+      <c r="J83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H83" s="18" t="inlineStr">
+      <c r="L83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="M83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I83" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J83" s="18" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="K83" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="L83" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="M83" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="N83" s="18" t="inlineStr">
+      <c r="N83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
@@ -6316,62 +6316,62 @@
           <t>0:2</t>
         </is>
       </c>
-      <c r="C84" s="18" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D84" s="18" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="E84" s="18" t="inlineStr">
+      <c r="H84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F84" s="17" t="inlineStr">
+      <c r="I84" s="17" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="G84" s="18" t="inlineStr">
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="K84" s="19" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="H84" s="18" t="inlineStr">
+      <c r="L84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="M84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I84" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J84" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K84" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L84" s="18" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="M84" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="N84" s="18" t="inlineStr">
+      <c r="N84" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
@@ -6393,57 +6393,57 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="E85" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F85" s="17" t="inlineStr">
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
+      <c r="J85" s="17" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="H85" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="M85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J85" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="N85" s="18" t="inlineStr">
+      <c r="N85" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
@@ -6511,42 +6511,42 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Timo Mayer</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Friedbert Mechler</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="L1" s="13" t="inlineStr">
@@ -6588,39 +6588,39 @@
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
         </is>
       </c>
       <c r="K3" s="20" t="inlineStr">
@@ -6734,22 +6734,22 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -6804,24 +6804,24 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
@@ -6955,22 +6955,22 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -7020,44 +7020,44 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr">
@@ -7097,24 +7097,24 @@
           <t>England</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
@@ -7236,44 +7236,44 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -7380,34 +7380,34 @@
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>Kanada</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
@@ -7524,44 +7524,44 @@
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr">
@@ -7752,39 +7752,39 @@
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -7819,29 +7819,29 @@
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Norwegen</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -7896,34 +7896,34 @@
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -7955,65 +7955,65 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J23" s="20" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="M23" s="20" t="inlineStr">
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="N23" s="20" t="inlineStr">
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -8035,57 +8035,57 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr">
+      <c r="L24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M24" s="20" t="inlineStr">
+      <c r="M24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="N24" s="20" t="inlineStr">
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -8099,52 +8099,52 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -8171,65 +8171,65 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="M26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="N26" s="20" t="inlineStr">
+      <c r="N26" s="17" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Schweiz</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -8256,39 +8256,39 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -8337,37 +8337,37 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -8409,22 +8409,22 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -8481,32 +8481,32 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -8548,42 +8548,42 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -8627,42 +8627,42 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -8704,37 +8704,37 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -8778,42 +8778,42 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="L37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -641,29 +641,29 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Egon Hejda</t>
+          <t>Myles Davies</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>0</v>
@@ -678,29 +678,29 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Myles Davies</t>
+          <t>Egon Hejda</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>0</v>
@@ -715,17 +715,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Christian Sandritter</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>295</v>
+        <v>357</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>109</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>55</v>
@@ -734,10 +734,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
@@ -752,17 +752,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Christian Sandritter</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>55</v>
@@ -771,7 +771,7 @@
         <v>50</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>0</v>
@@ -789,14 +789,14 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>81</v>
@@ -808,10 +808,10 @@
         <v>50</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0</v>
@@ -826,29 +826,29 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>60</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>0</v>
@@ -863,26 +863,26 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
@@ -900,17 +900,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Friedbert Mechler</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>55</v>
@@ -919,7 +919,7 @@
         <v>40</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>111</v>
@@ -956,7 +956,7 @@
         <v>40</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
@@ -974,26 +974,26 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Friedbert Mechler</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>102</v>
@@ -1030,7 +1030,7 @@
         <v>30</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>85</v>
@@ -1067,7 +1067,7 @@
         <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0</v>
@@ -1122,52 +1122,52 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
           <t>Egon Hejda</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
           <t>Timo Mayer</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -1201,60 +1201,60 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -1271,54 +1271,54 @@
           <t>2:1</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="M4" s="20" t="inlineStr">
@@ -1345,42 +1345,42 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>3:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>3:2  (+0)</t>
-        </is>
-      </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -1415,57 +1415,57 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>1:0  (+4)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M6" s="18" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -1489,52 +1489,52 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -1638,54 +1638,54 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -1712,52 +1712,52 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -1784,52 +1784,52 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -1854,54 +1854,54 @@
           <t>6:0</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="M13" s="19" t="inlineStr">
@@ -1926,54 +1926,54 @@
           <t>2:1</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
         </is>
       </c>
       <c r="M14" s="19" t="inlineStr">
@@ -1998,57 +1998,57 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
@@ -2077,54 +2077,54 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -2161,42 +2161,42 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
@@ -2223,52 +2223,52 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -2295,60 +2295,60 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>5:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>5:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="M20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
@@ -2375,44 +2375,44 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>0:3  (+4)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="M21" s="19" t="inlineStr">
@@ -2437,57 +2437,57 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -2516,62 +2516,62 @@
           <t>4:1</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>3:0  (+3)</t>
         </is>
@@ -2615,27 +2615,27 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -2662,52 +2662,52 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -2734,52 +2734,52 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -2806,55 +2806,55 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="K28" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="inlineStr">
+      <c r="M28" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -2878,52 +2878,52 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
           <t>3:2  (+0)</t>
         </is>
       </c>
-      <c r="I29" s="18" t="inlineStr">
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K29" s="20" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -2957,52 +2957,52 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>7:0  (+2)</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
         </is>
       </c>
       <c r="M31" s="19" t="inlineStr">
@@ -3029,55 +3029,55 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="J32" s="20" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="K32" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="M32" s="18" t="inlineStr">
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -3099,54 +3099,54 @@
           <t>2:1</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
+          <t>3:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>3:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="M33" s="19" t="inlineStr">
@@ -3173,52 +3173,52 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K34" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="M34" s="20" t="inlineStr">
@@ -3253,44 +3253,44 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>1:3  (+3)</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>0:7  (+2)</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="J35" s="18" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="J35" s="18" t="inlineStr">
-        <is>
-          <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>0:7  (+2)</t>
         </is>
       </c>
       <c r="M35" s="19" t="inlineStr">
@@ -3317,52 +3317,52 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="M36" s="20" t="inlineStr">
@@ -3394,57 +3394,57 @@
           <t>2:2</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>0:0  (+3)</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>2:2  (+4)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>2:2  (+4)</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J38" s="20" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K38" s="20" t="inlineStr">
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="inlineStr">
+      <c r="M38" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -3468,52 +3468,52 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I39" s="20" t="inlineStr">
+      <c r="J39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J39" s="20" t="inlineStr">
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="M39" s="19" t="inlineStr">
@@ -3540,37 +3540,37 @@
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="J40" s="19" t="inlineStr">
@@ -3612,52 +3612,52 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr">
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J41" s="20" t="inlineStr">
+      <c r="K41" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="M41" s="19" t="inlineStr">
@@ -3682,57 +3682,57 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H42" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J42" s="20" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K42" s="20" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M42" s="17" t="inlineStr">
+      <c r="M42" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
@@ -3756,55 +3756,55 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="L43" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="M43" s="17" t="inlineStr">
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
@@ -3835,52 +3835,52 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
           <t>3:2  (+0)</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J45" s="20" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K45" s="20" t="inlineStr">
+      <c r="L45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="M45" s="20" t="inlineStr">
@@ -3915,47 +3915,47 @@
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>0:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H46" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J46" s="20" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K46" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="M46" s="18" t="inlineStr">
+      <c r="M46" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -3989,42 +3989,42 @@
       </c>
       <c r="E47" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="M47" s="20" t="inlineStr">
@@ -4049,57 +4049,57 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>2:3  (+2)</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>2:3  (+2)</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="I48" s="20" t="inlineStr">
+      <c r="J48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J48" s="19" t="inlineStr">
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="K48" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M48" s="18" t="inlineStr">
+      <c r="M48" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -4123,55 +4123,55 @@
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="K49" s="20" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="L49" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="M49" s="17" t="inlineStr">
+      <c r="M49" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
@@ -4205,42 +4205,42 @@
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="K50" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="L50" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L50" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="M50" s="19" t="inlineStr">
@@ -4274,52 +4274,52 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>7:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>7:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H52" s="20" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
         </is>
       </c>
       <c r="M52" s="20" t="inlineStr">
@@ -4346,52 +4346,52 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="E53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
@@ -4428,50 +4428,50 @@
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="K54" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="K54" s="19" t="inlineStr">
+      <c r="M54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="N54" s="17" t="inlineStr">
+      <c r="N54" s="18" t="inlineStr">
         <is>
           <t>4:0  (+4)</t>
         </is>
@@ -4490,52 +4490,52 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="H55" s="20" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="J55" s="20" t="inlineStr">
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="M55" s="20" t="inlineStr">
@@ -4562,60 +4562,60 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="K56" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="M56" s="18" t="inlineStr">
+      <c r="M56" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="N56" s="18" t="inlineStr">
+      <c r="N56" s="17" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
@@ -4632,57 +4632,57 @@
           <t>0:1</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>2:4  (+2)</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>2:4  (+2)</t>
-        </is>
-      </c>
-      <c r="G57" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J57" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="K57" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L57" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
-        </is>
-      </c>
-      <c r="M57" s="18" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
@@ -4713,55 +4713,55 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
+          <t>3:1  (+4)</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>4:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="J59" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>4:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H59" s="17" t="inlineStr">
+      <c r="K59" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L59" s="18" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J59" s="17" t="inlineStr">
-        <is>
-          <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="K59" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L59" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M59" s="17" t="inlineStr">
+      <c r="M59" s="18" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
         </is>
@@ -4783,62 +4783,62 @@
           <t>1:4</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L60" s="18" t="inlineStr">
+      <c r="M60" s="17" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="M60" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="N60" s="17" t="inlineStr">
+      <c r="N60" s="18" t="inlineStr">
         <is>
           <t>1:4  (+4)</t>
         </is>
@@ -4855,62 +4855,62 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="E61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E61" s="19" t="inlineStr">
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="K61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="L61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="K61" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L61" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
       <c r="M61" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="N61" s="17" t="inlineStr">
+      <c r="N61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
@@ -4927,62 +4927,62 @@
           <t>3:2</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E62" s="19" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="H62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="I62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J62" s="18" t="inlineStr">
+      <c r="K62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="K62" s="18" t="inlineStr">
+      <c r="L62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
       <c r="M62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="N62" s="18" t="inlineStr">
+      <c r="N62" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
@@ -5001,60 +5001,60 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="M63" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K63" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L63" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="M63" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="N63" s="17" t="inlineStr">
+      <c r="N63" s="18" t="inlineStr">
         <is>
           <t>1:4  (+4)</t>
         </is>
@@ -5073,52 +5073,52 @@
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>5:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="G64" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
-        <is>
-          <t>5:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K64" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="M64" s="20" t="inlineStr">
@@ -5150,54 +5150,54 @@
           <t>3:0</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J66" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="E66" s="19" t="inlineStr">
+      <c r="K66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G66" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J66" s="18" t="inlineStr">
+      <c r="L66" s="17" t="inlineStr">
         <is>
           <t>4:1  (+3)</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M66" s="19" t="inlineStr">
@@ -5222,44 +5222,44 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="J67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="K67" s="19" t="inlineStr">
@@ -5294,47 +5294,47 @@
           <t>2:0</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>3:2  (+2)</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>3:2  (+2)</t>
-        </is>
-      </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H68" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J68" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K68" s="18" t="inlineStr">
+      <c r="K68" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -5366,54 +5366,54 @@
           <t>1:2</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>1:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>1:3  (+2)</t>
-        </is>
-      </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
+          <t>1:2  (+4)</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
           <t>0:1  (+3)</t>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L69" s="18" t="inlineStr">
         <is>
           <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="G69" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J69" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+4)</t>
-        </is>
-      </c>
-      <c r="K69" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L69" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
         </is>
       </c>
       <c r="M69" s="20" t="inlineStr">
@@ -5440,52 +5440,52 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="D70" s="20" t="inlineStr">
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>2:4  (+0)</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>2:3  (+0)</t>
+        </is>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>2:4  (+0)</t>
-        </is>
-      </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
-        <is>
-          <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="K70" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="M70" s="20" t="inlineStr">
@@ -5510,62 +5510,62 @@
           <t>1:3</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E71" s="19" t="inlineStr">
+      <c r="H71" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="G71" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H71" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
+      <c r="K71" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="L71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="J71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K71" s="19" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="L71" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="M71" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="N71" s="18" t="inlineStr">
+      <c r="N71" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
@@ -5591,52 +5591,52 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="E73" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G73" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L73" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="M73" s="20" t="inlineStr">
@@ -5663,52 +5663,52 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
           <t>1:3  (+4)</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>1:3  (+4)</t>
+        </is>
+      </c>
+      <c r="F74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="E74" s="19" t="inlineStr">
+      <c r="K74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L74" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M74" s="20" t="inlineStr">
@@ -5735,52 +5735,52 @@
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="D75" s="19" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="L75" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="E75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="K75" s="17" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="L75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="M75" s="19" t="inlineStr">
@@ -5805,54 +5805,54 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="D76" s="19" t="inlineStr">
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="E76" s="19" t="inlineStr">
+      <c r="H76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F76" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
+      <c r="I76" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="I76" s="19" t="inlineStr">
+      <c r="J76" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="J76" s="19" t="inlineStr">
+      <c r="K76" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L76" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K76" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="M76" s="19" t="inlineStr">
@@ -5877,57 +5877,57 @@
           <t>0:0</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
+          <t>2:2  (+3)</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
           <t>0:0  (+4)</t>
         </is>
       </c>
-      <c r="F77" s="18" t="inlineStr">
-        <is>
-          <t>2:2  (+3)</t>
-        </is>
-      </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I77" s="20" t="inlineStr">
+      <c r="J77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="J77" s="20" t="inlineStr">
+      <c r="K77" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="K77" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="L77" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="M77" s="18" t="inlineStr">
+      <c r="M77" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
@@ -5949,16 +5949,16 @@
           <t>3:1</t>
         </is>
       </c>
-      <c r="C78" s="18" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>4:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D78" s="19" t="inlineStr">
-        <is>
-          <t>4:3  (+2)</t>
-        </is>
-      </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
@@ -5966,37 +5966,37 @@
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H78" s="18" t="inlineStr">
+      <c r="H78" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I78" s="20" t="inlineStr">
+      <c r="J78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="J78" s="20" t="inlineStr">
+      <c r="K78" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="K78" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="L78" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
       <c r="M78" s="20" t="inlineStr">
@@ -6028,62 +6028,62 @@
           <t>4:2</t>
         </is>
       </c>
-      <c r="C80" s="18" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="D80" s="19" t="inlineStr">
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G80" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>3:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J80" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="F80" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G80" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H80" s="18" t="inlineStr">
+      <c r="K80" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="I80" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J80" s="18" t="inlineStr">
+      <c r="L80" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="K80" s="18" t="inlineStr">
-        <is>
-          <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="L80" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
-        </is>
-      </c>
       <c r="M80" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="N80" s="18" t="inlineStr">
+      <c r="N80" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
         </is>
@@ -6100,62 +6100,62 @@
           <t>1:0</t>
         </is>
       </c>
-      <c r="C81" s="19" t="inlineStr">
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>1:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="M81" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="F81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J81" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="L81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="M81" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="N81" s="18" t="inlineStr">
+      <c r="N81" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
         </is>
@@ -6174,52 +6174,52 @@
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
-        </is>
-      </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G82" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H82" s="20" t="inlineStr">
+      <c r="I82" s="20" t="inlineStr">
         <is>
           <t>4:2  (+0)</t>
         </is>
       </c>
-      <c r="I82" s="20" t="inlineStr">
+      <c r="J82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="J82" s="20" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="K82" s="20" t="inlineStr">
+      <c r="L82" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="L82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="M82" s="20" t="inlineStr">
@@ -6246,52 +6246,52 @@
       </c>
       <c r="C83" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="D83" s="19" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="E83" s="19" t="inlineStr">
+      <c r="H83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F83" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
-        </is>
-      </c>
-      <c r="G83" s="18" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="J83" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="L83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I83" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="K83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="L83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="M83" s="19" t="inlineStr">
@@ -6318,52 +6318,52 @@
       </c>
       <c r="C84" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="D84" s="19" t="inlineStr">
+      <c r="E84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="F84" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="F84" s="19" t="inlineStr">
+      <c r="H84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="I84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G84" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
-        </is>
-      </c>
-      <c r="H84" s="19" t="inlineStr">
+      <c r="J84" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="K84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="L84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="J84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="K84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
-        </is>
-      </c>
-      <c r="L84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
         </is>
       </c>
       <c r="M84" s="19" t="inlineStr">
@@ -6388,52 +6388,52 @@
           <t>2:1</t>
         </is>
       </c>
-      <c r="C85" s="20" t="inlineStr">
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="inlineStr">
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="F85" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G85" s="20" t="inlineStr">
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H85" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
+      <c r="J85" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="J85" s="17" t="inlineStr">
+      <c r="K85" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="K85" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="L85" s="17" t="inlineStr">
+      <c r="L85" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
@@ -6506,52 +6506,52 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
+          <t>Myles Davies</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
           <t>Egon Hejda</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Myles Davies</t>
-        </is>
-      </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
+          <t>Christian Sandritter</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Norman Urbanetz</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Christian Sandritter</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Norman Urbanetz</t>
-        </is>
-      </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
           <t>Timo Mayer</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Marco Schirmacher</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Friedbert Mechler</t>
-        </is>
-      </c>
-      <c r="K1" s="13" t="inlineStr">
-        <is>
-          <t>Marco Schirmacher</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
@@ -6583,62 +6583,62 @@
           <t>Kanada</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Südkorea</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>Kanada</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="K3" s="20" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
-        </is>
-      </c>
-      <c r="M3" s="17" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -6655,62 +6655,62 @@
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -6814,14 +6814,14 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Marokko</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -6871,62 +6871,62 @@
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
@@ -6943,62 +6943,62 @@
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="L8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -7015,42 +7015,42 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Südkorea</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -7060,7 +7060,7 @@
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
@@ -7087,62 +7087,62 @@
           <t>England</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -7159,62 +7159,62 @@
           <t>Belgien</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
@@ -7231,62 +7231,62 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -7303,62 +7303,62 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -7375,54 +7375,54 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -7447,62 +7447,62 @@
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>Kanada</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
@@ -7519,57 +7519,57 @@
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Ägypten</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Ägypten</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
@@ -7591,62 +7591,62 @@
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -7663,62 +7663,62 @@
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="18" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -7742,47 +7742,47 @@
           <t>Marokko</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
@@ -7816,27 +7816,27 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>Marokko</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -7886,29 +7886,29 @@
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -7958,62 +7958,62 @@
           <t>England</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="L23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -8030,62 +8030,62 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -8102,54 +8102,54 @@
           <t>Belgien</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -8174,62 +8174,62 @@
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="K26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J26" s="20" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="M26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
@@ -8256,44 +8256,44 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="L27" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -8322,65 +8322,65 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="J29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="K29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
+      <c r="M29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="M29" s="21" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
+      <c r="N29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
@@ -8394,65 +8394,65 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="K30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="L30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="K30" s="21" t="inlineStr">
+      <c r="M30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="L30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M30" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="N30" s="21" t="inlineStr">
+      <c r="N30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
@@ -8466,65 +8466,65 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
+      <c r="N31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -8538,65 +8538,65 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>Schweiz</t>
         </is>
       </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="M32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
+      <c r="N32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -8617,65 +8617,65 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="inlineStr">
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="N34" s="21" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
@@ -8692,62 +8692,62 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="M35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="N35" s="21" t="inlineStr">
+      <c r="N35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
@@ -8788,37 +8788,37 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="J37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>113</v>
@@ -666,7 +666,7 @@
         <v>20</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0</v>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>113</v>
@@ -666,7 +666,7 @@
         <v>20</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0</v>

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -789,26 +789,26 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>55</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>20</v>
@@ -826,26 +826,26 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" s="7" t="n">
         <v>30</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>45</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>20</v>
@@ -863,29 +863,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Timo Mayer</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>60</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>45</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -900,23 +900,23 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Timo Mayer</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>45</v>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="G1" s="13" t="inlineStr">
         <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Edgar Mayer</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
@@ -1219,24 +1219,24 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
         </is>
       </c>
       <c r="K3" s="18" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K4" s="18" t="inlineStr">
@@ -1363,24 +1363,24 @@
           <t>3:2  (+0)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -1435,19 +1435,19 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="K7" s="19" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -1663,19 +1663,19 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>0:3  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -1802,24 +1802,24 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="K12" s="19" t="inlineStr">
@@ -1874,24 +1874,24 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
       <c r="K13" s="19" t="inlineStr">
@@ -1946,19 +1946,19 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>4:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -2023,19 +2023,19 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -2099,22 +2099,22 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -2171,22 +2171,22 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>1:4  (+2)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="K18" s="19" t="inlineStr">
@@ -2246,19 +2246,19 @@
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -2315,22 +2315,22 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
           <t>5:1  (+2)</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
@@ -2385,24 +2385,24 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>0:3  (+4)</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="K21" s="19" t="inlineStr">
@@ -2457,19 +2457,19 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
@@ -2546,14 +2546,14 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -2610,22 +2610,22 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -2680,24 +2680,24 @@
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -2754,17 +2754,17 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="K28" s="19" t="inlineStr">
@@ -2896,24 +2896,24 @@
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>3:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
           <t>7:0  (+2)</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>5:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="J31" s="19" t="inlineStr">
@@ -3057,14 +3057,14 @@
           <t>2:1  (+3)</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -3193,22 +3193,22 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
         </is>
       </c>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="K34" s="20" t="inlineStr">
@@ -3263,24 +3263,24 @@
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
         <is>
           <t>0:7  (+2)</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>1:3  (+3)</t>
-        </is>
-      </c>
-      <c r="J35" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
         </is>
       </c>
       <c r="K35" s="19" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="I36" s="20" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J36" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="K36" s="20" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -3486,24 +3486,24 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="I39" s="20" t="inlineStr">
+      <c r="J39" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J39" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K39" s="20" t="inlineStr">
@@ -3568,14 +3568,14 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I40" s="20" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="K40" s="19" t="inlineStr">
@@ -3630,24 +3630,24 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J41" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K41" s="19" t="inlineStr">
@@ -3707,19 +3707,19 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I42" s="20" t="inlineStr">
+      <c r="J42" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J42" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="K42" s="20" t="inlineStr">
@@ -3776,22 +3776,22 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="J43" s="18" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="K43" s="17" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="I45" s="20" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>3:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="K45" s="20" t="inlineStr">
@@ -3930,19 +3930,19 @@
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J46" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="K46" s="20" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
           <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="K47" s="20" t="inlineStr">
@@ -4074,19 +4074,19 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="H48" s="19" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J48" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K48" s="18" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="K49" s="20" t="inlineStr">
@@ -4215,22 +4215,22 @@
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H50" s="19" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="G52" s="20" t="inlineStr">
         <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="H52" s="20" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>6:0  (+0)</t>
         </is>
       </c>
-      <c r="I52" s="20" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J52" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
         </is>
       </c>
       <c r="K52" s="20" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="K53" s="20" t="inlineStr">
@@ -4438,22 +4438,22 @@
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="K54" s="19" t="inlineStr">
@@ -4510,22 +4510,22 @@
       </c>
       <c r="G55" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
         </is>
       </c>
-      <c r="H55" s="20" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>3:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="K55" s="20" t="inlineStr">
@@ -4582,22 +4582,22 @@
       </c>
       <c r="G56" s="20" t="inlineStr">
         <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
           <t>0:4  (+0)</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
+      <c r="I56" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="I56" s="20" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J56" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="K56" s="20" t="inlineStr">
@@ -4652,24 +4652,24 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>0:1  (+4)</t>
         </is>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="J57" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="K57" s="19" t="inlineStr">
@@ -4736,19 +4736,19 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="I59" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="I59" s="18" t="inlineStr">
+      <c r="J59" s="18" t="inlineStr">
         <is>
           <t>3:1  (+4)</t>
-        </is>
-      </c>
-      <c r="J59" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="K59" s="19" t="inlineStr">
@@ -4803,24 +4803,24 @@
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="I60" s="17" t="inlineStr">
         <is>
           <t>0:3  (+3)</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
         </is>
       </c>
       <c r="K60" s="19" t="inlineStr">
@@ -4875,24 +4875,24 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="19" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J61" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
         </is>
       </c>
       <c r="K61" s="18" t="inlineStr">
@@ -4947,24 +4947,24 @@
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H62" s="20" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="I62" s="17" t="inlineStr">
+      <c r="J62" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J62" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K62" s="17" t="inlineStr">
@@ -5019,24 +5019,24 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G63" s="20" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="H63" s="19" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="I63" s="20" t="inlineStr">
+      <c r="J63" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="K63" s="19" t="inlineStr">
@@ -5091,14 +5091,14 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
@@ -5170,24 +5170,24 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="I66" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="J66" s="19" t="inlineStr">
         <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J66" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
         </is>
       </c>
       <c r="K66" s="19" t="inlineStr">
@@ -5242,19 +5242,19 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H67" s="19" t="inlineStr">
+      <c r="I67" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="J67" s="17" t="inlineStr">
@@ -5314,24 +5314,24 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G68" s="18" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
         </is>
       </c>
-      <c r="H68" s="20" t="inlineStr">
+      <c r="I68" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="I68" s="20" t="inlineStr">
+      <c r="J68" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="K68" s="17" t="inlineStr">
@@ -5458,24 +5458,24 @@
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="G70" s="20" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="I70" s="20" t="inlineStr">
         <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="I70" s="20" t="inlineStr">
+      <c r="J70" s="20" t="inlineStr">
         <is>
           <t>2:3  (+0)</t>
-        </is>
-      </c>
-      <c r="J70" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
         </is>
       </c>
       <c r="K70" s="20" t="inlineStr">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="H71" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
+        <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="I71" s="18" t="inlineStr">
+      <c r="J71" s="18" t="inlineStr">
         <is>
           <t>1:3  (+4)</t>
-        </is>
-      </c>
-      <c r="J71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="K71" s="19" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I73" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="K73" s="20" t="inlineStr">
@@ -5681,24 +5681,24 @@
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="H74" s="19" t="inlineStr">
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I74" s="19" t="inlineStr">
+      <c r="J74" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
         </is>
       </c>
       <c r="K74" s="19" t="inlineStr">
@@ -5753,24 +5753,24 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G75" s="19" t="inlineStr">
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>5:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="H75" s="19" t="inlineStr">
+      <c r="I75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="I75" s="19" t="inlineStr">
+      <c r="J75" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>5:0  (+4)</t>
         </is>
       </c>
       <c r="K75" s="18" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
           <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="K76" s="19" t="inlineStr">
@@ -5897,19 +5897,19 @@
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="G77" s="18" t="inlineStr">
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>0:0  (+4)</t>
         </is>
       </c>
-      <c r="H77" s="20" t="inlineStr">
+      <c r="I77" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
@@ -5971,22 +5971,22 @@
       </c>
       <c r="G78" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="H78" s="19" t="inlineStr">
+      <c r="I78" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="I78" s="17" t="inlineStr">
+      <c r="J78" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="J78" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K78" s="20" t="inlineStr">
@@ -6048,24 +6048,24 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G80" s="20" t="inlineStr">
+      <c r="G80" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="H80" s="17" t="inlineStr">
+      <c r="I80" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="I80" s="17" t="inlineStr">
+      <c r="J80" s="17" t="inlineStr">
         <is>
           <t>3:1  (+3)</t>
-        </is>
-      </c>
-      <c r="J80" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr">
@@ -6122,22 +6122,22 @@
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
+        <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="H81" s="19" t="inlineStr">
+      <c r="I81" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="I81" s="19" t="inlineStr">
+      <c r="J81" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="J81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="K81" s="19" t="inlineStr">
@@ -6194,22 +6194,22 @@
       </c>
       <c r="G82" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="H82" s="20" t="inlineStr">
+      <c r="I82" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="I82" s="20" t="inlineStr">
+      <c r="J82" s="20" t="inlineStr">
         <is>
           <t>4:2  (+0)</t>
-        </is>
-      </c>
-      <c r="J82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="K82" s="20" t="inlineStr">
@@ -6264,24 +6264,24 @@
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G83" s="19" t="inlineStr">
+      <c r="G83" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="I83" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="I83" s="19" t="inlineStr">
+      <c r="J83" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="J83" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="K83" s="19" t="inlineStr">
@@ -6336,24 +6336,24 @@
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="G84" s="19" t="inlineStr">
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>0:2  (+4)</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="H84" s="19" t="inlineStr">
+      <c r="I84" s="19" t="inlineStr">
         <is>
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="I84" s="19" t="inlineStr">
+      <c r="J84" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="J84" s="18" t="inlineStr">
-        <is>
-          <t>0:2  (+4)</t>
         </is>
       </c>
       <c r="K84" s="19" t="inlineStr">
@@ -6408,24 +6408,24 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G85" s="17" t="inlineStr">
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="H85" s="18" t="inlineStr">
+      <c r="I85" s="18" t="inlineStr">
         <is>
           <t>2:1  (+4)</t>
         </is>
       </c>
-      <c r="I85" s="20" t="inlineStr">
+      <c r="J85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="J85" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="K85" s="18" t="inlineStr">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="G1" s="13" t="inlineStr">
         <is>
+          <t>Stefan Seiler</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Markus Bruckner</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Edgar Mayer</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Timo Mayer</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
-        <is>
-          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
@@ -6603,24 +6603,24 @@
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>Kanada</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>Bosnien-Herzegowina</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t>Kanada</t>
         </is>
       </c>
       <c r="K3" s="20" t="inlineStr">
@@ -6891,24 +6891,24 @@
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Elfenbeinküste</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>Elfenbeinküste</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -7107,14 +7107,14 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -7251,19 +7251,19 @@
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Senegal</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -7395,24 +7395,24 @@
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>Kolumbien</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
           <t>Kanada</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="K15" s="18" t="inlineStr">
@@ -7539,24 +7539,24 @@
           <t>Belgien</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="K16" s="18" t="inlineStr">
@@ -7762,19 +7762,19 @@
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="J20" s="18" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -7906,14 +7906,14 @@
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -7978,14 +7978,14 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8122,24 +8122,24 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="J25" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
           <t>Schweiz</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -8266,14 +8266,14 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -8345,19 +8345,19 @@
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="J29" s="18" t="inlineStr">
@@ -8417,14 +8417,14 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>Norwegen</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -8489,24 +8489,24 @@
           <t>England</t>
         </is>
       </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="J31" s="18" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -8571,14 +8571,14 @@
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -8642,17 +8642,17 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Argentinien</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -8714,22 +8714,22 @@
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I35" s="20" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="J35" s="20" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="K35" s="20" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">

--- a/Rangliste.xlsx
+++ b/Rangliste.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,9 +192,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -645,7 +642,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>113</v>
@@ -669,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -682,7 +679,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>120</v>
@@ -706,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -719,7 +716,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>109</v>
@@ -743,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -752,14 +749,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Norman Urbanetz</t>
+          <t>Markus Bruckner</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>81</v>
@@ -771,16 +768,16 @@
         <v>50</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -789,23 +786,23 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Stefan Seiler</t>
+          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>75</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>45</v>
@@ -817,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -826,14 +823,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Markus Bruckner</t>
+          <t>Norman Urbanetz</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>81</v>
@@ -845,10 +842,10 @@
         <v>50</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>0</v>
@@ -863,23 +860,23 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Edgar Mayer</t>
+          <t>Stefan Seiler</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>75</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>45</v>
@@ -1137,22 +1134,22 @@
       </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="J1" s="13" t="inlineStr">
@@ -1219,19 +1216,19 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
       <c r="J3" s="17" t="inlineStr">
@@ -1286,24 +1283,24 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>1:0  (+3)</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="J4" s="19" t="inlineStr">
@@ -1360,22 +1357,22 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
           <t>3:2  (+0)</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -1430,24 +1427,24 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -1502,24 +1499,24 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -1576,22 +1573,22 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -1658,19 +1655,19 @@
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -1732,17 +1729,17 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
+          <t>0:3  (+0)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>0:3  (+0)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -1802,19 +1799,19 @@
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="J12" s="19" t="inlineStr">
@@ -1869,24 +1866,24 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
@@ -1941,24 +1938,24 @@
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>4:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>4:1  (+2)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -2013,24 +2010,24 @@
           <t>3:1  (+4)</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -2094,22 +2091,22 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
           <t>2:0  (+0)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -2164,24 +2161,24 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>1:4  (+2)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>1:4  (+2)</t>
         </is>
       </c>
       <c r="J18" s="17" t="inlineStr">
@@ -2236,24 +2233,24 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>0:1  (+4)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -2310,22 +2307,22 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
+          <t>5:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>3:0  (+4)</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
           <t>4:0  (+2)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>4:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>5:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>3:0  (+4)</t>
         </is>
       </c>
       <c r="J20" s="18" t="inlineStr">
@@ -2380,24 +2377,24 @@
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>0:3  (+4)</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>0:3  (+4)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="J21" s="19" t="inlineStr">
@@ -2457,19 +2454,19 @@
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
@@ -2533,17 +2530,17 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -2610,17 +2607,17 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -2675,19 +2672,19 @@
           <t>3:1  (+3)</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>1:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -2749,22 +2746,22 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -2824,19 +2821,19 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>2:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
@@ -2893,22 +2890,22 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -2972,22 +2969,22 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
+          <t>7:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
           <t>5:0  (+2)</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>5:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>7:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>5:0  (+2)</t>
         </is>
       </c>
       <c r="J31" s="19" t="inlineStr">
@@ -3042,19 +3039,19 @@
           <t>2:3  (+0)</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>2:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>2:1  (+3)</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
@@ -3114,19 +3111,19 @@
           <t>3:2  (+3)</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -3188,22 +3185,22 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -3258,24 +3255,24 @@
           <t>1:3  (+3)</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>0:7  (+2)</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>0:7  (+2)</t>
         </is>
       </c>
       <c r="J35" s="17" t="inlineStr">
@@ -3411,22 +3408,22 @@
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -3483,22 +3480,22 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G39" s="20" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
@@ -3555,17 +3552,17 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="I40" s="19" t="inlineStr">
@@ -3630,19 +3627,19 @@
           <t>0:2  (+2)</t>
         </is>
       </c>
-      <c r="G41" s="20" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
         </is>
       </c>
       <c r="J41" s="19" t="inlineStr">
@@ -3697,24 +3694,24 @@
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>1:1  (+4)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H42" s="18" t="inlineStr">
-        <is>
-          <t>1:1  (+4)</t>
-        </is>
-      </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="J42" s="20" t="inlineStr">
@@ -3771,22 +3768,22 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>0:2  (+3)</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>0:2  (+3)</t>
         </is>
       </c>
       <c r="J43" s="18" t="inlineStr">
@@ -3850,22 +3847,22 @@
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
+          <t>3:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>1:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>3:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>1:0  (+0)</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
@@ -3922,22 +3919,22 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
+          <t>1:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
           <t>0:0  (+3)</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="I46" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr">
@@ -4064,24 +4061,24 @@
           <t>2:3  (+2)</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="G48" s="20" t="inlineStr">
+      <c r="I48" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
@@ -4143,17 +4140,17 @@
       </c>
       <c r="G49" s="20" t="inlineStr">
         <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
           <t>1:0  (+0)</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
         <is>
           <t>1:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
         </is>
       </c>
       <c r="J49" s="20" t="inlineStr">
@@ -4215,17 +4212,17 @@
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
@@ -4294,17 +4291,17 @@
       </c>
       <c r="G52" s="20" t="inlineStr">
         <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>6:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
           <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t>6:0  (+0)</t>
         </is>
       </c>
       <c r="J52" s="20" t="inlineStr">
@@ -4361,17 +4358,17 @@
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
@@ -4433,22 +4430,22 @@
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
+        <is>
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G54" s="19" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
@@ -4505,22 +4502,22 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
+          <t>5:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>3:0  (+0)</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>2:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>5:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>3:0  (+0)</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
@@ -4582,17 +4579,17 @@
       </c>
       <c r="G56" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>0:4  (+0)</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>0:4  (+0)</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr">
@@ -4647,24 +4644,24 @@
           <t>2:4  (+2)</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>1:2  (+3)</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>0:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H57" s="17" t="inlineStr">
-        <is>
-          <t>1:2  (+3)</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>0:1  (+4)</t>
         </is>
       </c>
       <c r="J57" s="17" t="inlineStr">
@@ -4731,19 +4728,19 @@
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="H59" s="17" t="inlineStr">
+      <c r="I59" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="I59" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
         </is>
       </c>
       <c r="J59" s="18" t="inlineStr">
@@ -4798,24 +4795,24 @@
           <t>0:1  (+2)</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>0:3  (+3)</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>1:2  (+2)</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>0:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H60" s="17" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
-        </is>
-      </c>
-      <c r="I60" s="17" t="inlineStr">
-        <is>
-          <t>0:3  (+3)</t>
         </is>
       </c>
       <c r="J60" s="19" t="inlineStr">
@@ -4870,24 +4867,24 @@
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="F61" s="18" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>3:1  (+2)</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
         </is>
       </c>
-      <c r="G61" s="18" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>3:1  (+2)</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="J61" s="19" t="inlineStr">
@@ -4942,24 +4939,24 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>2:2  (+0)</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
         <is>
           <t>0:2  (+0)</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I62" s="20" t="inlineStr">
-        <is>
-          <t>2:2  (+0)</t>
         </is>
       </c>
       <c r="J62" s="17" t="inlineStr">
@@ -5014,24 +5011,24 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>0:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>1:3  (+2)</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>0:1  (+2)</t>
         </is>
       </c>
       <c r="J63" s="20" t="inlineStr">
@@ -5086,19 +5083,19 @@
           <t>5:2  (+2)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>2:1  (+2)</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H64" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
@@ -5167,22 +5164,22 @@
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G66" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>3:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I66" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="J66" s="19" t="inlineStr">
@@ -5237,24 +5234,24 @@
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="F67" s="17" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
+      <c r="I67" s="17" t="inlineStr">
         <is>
           <t>2:0  (+3)</t>
-        </is>
-      </c>
-      <c r="H67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I67" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="J67" s="17" t="inlineStr">
@@ -5309,24 +5306,24 @@
           <t>3:2  (+2)</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>2:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>1:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="I68" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H68" s="18" t="inlineStr">
-        <is>
-          <t>2:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
-        <is>
-          <t>1:1  (+0)</t>
         </is>
       </c>
       <c r="J68" s="20" t="inlineStr">
@@ -5381,19 +5378,19 @@
           <t>1:2  (+4)</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>0:1  (+3)</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H69" s="17" t="inlineStr">
-        <is>
-          <t>0:1  (+3)</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
@@ -5455,22 +5452,22 @@
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
+          <t>0:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
           <t>1:3  (+0)</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>1:3  (+0)</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="H70" s="20" t="inlineStr">
-        <is>
-          <t>0:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
-        <is>
-          <t>1:3  (+0)</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
@@ -5525,24 +5522,24 @@
           <t>0:5  (+2)</t>
         </is>
       </c>
-      <c r="F71" s="17" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>0:4  (+2)</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
         <is>
           <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>0:4  (+2)</t>
         </is>
       </c>
       <c r="J71" s="18" t="inlineStr">
@@ -5606,22 +5603,22 @@
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
+          <t>4:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
           <t>3:0  (+0)</t>
         </is>
       </c>
-      <c r="G73" s="20" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>4:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
@@ -5678,22 +5675,22 @@
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
+          <t>1:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
           <t>0:3  (+2)</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>0:2  (+3)</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>1:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="J74" s="19" t="inlineStr">
@@ -5753,19 +5750,19 @@
           <t>2:0  (+2)</t>
         </is>
       </c>
-      <c r="G75" s="18" t="inlineStr">
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>4:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
         <is>
           <t>5:0  (+4)</t>
-        </is>
-      </c>
-      <c r="H75" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>4:0  (+2)</t>
         </is>
       </c>
       <c r="J75" s="19" t="inlineStr">
@@ -5820,19 +5817,19 @@
           <t>4:1  (+2)</t>
         </is>
       </c>
-      <c r="F76" s="17" t="inlineStr">
+      <c r="F76" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
         <is>
           <t>2:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
@@ -5892,24 +5889,24 @@
           <t>2:2  (+3)</t>
         </is>
       </c>
-      <c r="F77" s="17" t="inlineStr">
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>0:0  (+4)</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>0:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
         </is>
       </c>
-      <c r="G77" s="20" t="inlineStr">
+      <c r="I77" s="20" t="inlineStr">
         <is>
           <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>0:0  (+4)</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>0:1  (+0)</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
@@ -5966,22 +5963,22 @@
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
+          <t>0:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>1:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
           <t>0:1  (+0)</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="I78" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H78" s="20" t="inlineStr">
-        <is>
-          <t>0:0  (+0)</t>
-        </is>
-      </c>
-      <c r="I78" s="19" t="inlineStr">
-        <is>
-          <t>1:0  (+2)</t>
         </is>
       </c>
       <c r="J78" s="17" t="inlineStr">
@@ -6043,24 +6040,24 @@
           <t>1:1  (+0)</t>
         </is>
       </c>
-      <c r="F80" s="19" t="inlineStr">
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>1:2  (+0)</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>2:0  (+3)</t>
+        </is>
+      </c>
+      <c r="H80" s="19" t="inlineStr">
         <is>
           <t>3:0  (+2)</t>
         </is>
       </c>
-      <c r="G80" s="19" t="inlineStr">
+      <c r="I80" s="19" t="inlineStr">
         <is>
           <t>2:1  (+2)</t>
-        </is>
-      </c>
-      <c r="H80" s="20" t="inlineStr">
-        <is>
-          <t>1:2  (+0)</t>
-        </is>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>2:0  (+3)</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
@@ -6115,19 +6112,19 @@
           <t>3:1  (+2)</t>
         </is>
       </c>
-      <c r="F81" s="18" t="inlineStr">
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>3:0  (+2)</t>
+        </is>
+      </c>
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>2:0  (+2)</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
         <is>
           <t>1:0  (+4)</t>
-        </is>
-      </c>
-      <c r="G81" s="19" t="inlineStr">
-        <is>
-          <t>2:0  (+2)</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>3:0  (+2)</t>
         </is>
       </c>
       <c r="I81" s="19" t="inlineStr">
@@ -6187,19 +6184,19 @@
           <t>2:1  (+0)</t>
         </is>
       </c>
-      <c r="F82" s="17" t="inlineStr">
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>2:0  (+0)</t>
+        </is>
+      </c>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
+          <t>2:1  (+0)</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
         <is>
           <t>1:1  (+3)</t>
-        </is>
-      </c>
-      <c r="G82" s="20" t="inlineStr">
-        <is>
-          <t>2:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H82" s="20" t="inlineStr">
-        <is>
-          <t>2:0  (+0)</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -6259,24 +6256,24 @@
           <t>1:4  (+2)</t>
         </is>
       </c>
-      <c r="F83" s="17" t="inlineStr">
+      <c r="F83" s="19" t="inlineStr">
+        <is>
+          <t>0:2  (+2)</t>
+        </is>
+      </c>
+      <c r="G83" s="19" t="inlineStr">
+        <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr">
         <is>
           <t>1:2  (+3)</t>
         </is>
       </c>
-      <c r="G83" s="20" t="inlineStr">
+      <c r="I83" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="H83" s="19" t="inlineStr">
-        <is>
-          <t>0:2  (+2)</t>
-        </is>
-      </c>
-      <c r="I83" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
         </is>
       </c>
       <c r="J83" s="19" t="inlineStr">
@@ -6333,22 +6330,22 @@
       </c>
       <c r="F84" s="19" t="inlineStr">
         <is>
+          <t>0:3  (+2)</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="inlineStr">
+        <is>
+          <t>0:5  (+2)</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
+        <is>
           <t>0:4  (+2)</t>
         </is>
       </c>
-      <c r="G84" s="18" t="inlineStr">
+      <c r="I84" s="18" t="inlineStr">
         <is>
           <t>0:2  (+4)</t>
-        </is>
-      </c>
-      <c r="H84" s="19" t="inlineStr">
-        <is>
-          <t>0:3  (+2)</t>
-        </is>
-      </c>
-      <c r="I84" s="19" t="inlineStr">
-        <is>
-          <t>0:5  (+2)</t>
         </is>
       </c>
       <c r="J84" s="19" t="inlineStr">
@@ -6403,19 +6400,19 @@
           <t>2:2  (+0)</t>
         </is>
       </c>
-      <c r="F85" s="20" t="inlineStr">
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>1:0  (+3)</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>2:1  (+4)</t>
+        </is>
+      </c>
+      <c r="H85" s="20" t="inlineStr">
         <is>
           <t>1:1  (+0)</t>
-        </is>
-      </c>
-      <c r="G85" s="18" t="inlineStr">
-        <is>
-          <t>2:1  (+4)</t>
-        </is>
-      </c>
-      <c r="H85" s="17" t="inlineStr">
-        <is>
-          <t>1:0  (+3)</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
@@ -6521,22 +6518,22 @@
       </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
+          <t>Markus Bruckner</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Edgar Mayer</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Norman Urbanetz</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Stefan Seiler</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Markus Bruckner</t>
-        </is>
-      </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Edgar Mayer</t>
         </is>
       </c>
       <c r="J1" s="13" t="inlineStr">
@@ -6603,19 +6600,19 @@
           <t>Tschechien</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Bosnien-Herzegowina</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Tschechien</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Kanada</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Tschechien</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Bosnien-Herzegowina</t>
         </is>
       </c>
       <c r="J3" s="18" t="inlineStr">
@@ -6744,17 +6741,17 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -6814,19 +6811,19 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>Marokko</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -6886,24 +6883,24 @@
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Elfenbeinküste</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -6960,17 +6957,17 @@
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -7030,19 +7027,19 @@
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Südkorea</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -7102,19 +7099,19 @@
           <t>England</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>Kroatien</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>Kroatien</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -7176,17 +7173,17 @@
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
           <t>Mexiko</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>Belgien</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -7246,24 +7243,24 @@
           <t>Elfenbeinküste</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -7392,22 +7389,22 @@
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
           <t>Kolumbien</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Kolumbien</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>Kroatien</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>Kolumbien</t>
         </is>
       </c>
       <c r="J14" s="18" t="inlineStr">
@@ -7534,19 +7531,19 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Türkei</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>Belgien</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>Türkei</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -7757,24 +7754,24 @@
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="J20" s="18" t="inlineStr">
@@ -7829,19 +7826,19 @@
           <t>Niederlande</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>Marokko</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>Niederlande</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -7901,19 +7898,19 @@
           <t>Norwegen</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -7973,19 +7970,19 @@
           <t>England</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Mexiko</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>England</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>Mexiko</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -8047,17 +8044,17 @@
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>Belgien</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8117,24 +8114,24 @@
           <t>Belgien</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Mexiko</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>Türkei</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>Senegal</t>
         </is>
       </c>
       <c r="J25" s="18" t="inlineStr">
@@ -8191,17 +8188,17 @@
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
           <t>Argentinien</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>Schweiz</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -8261,19 +8258,19 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Argentinien</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>Argentinien</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -8340,24 +8337,24 @@
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
         </is>
       </c>
       <c r="J29" s="18" t="inlineStr">
@@ -8412,19 +8409,19 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Norwegen</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>Norwegen</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -8486,22 +8483,22 @@
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="J31" s="18" t="inlineStr">
@@ -8637,22 +8634,22 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>Brasilien</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -8707,24 +8704,24 @@
           <t>England</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>Argentinien</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -8768,65 +8765,65 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Spanien</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="K37" s="21" t="inlineStr">
+      <c r="K37" s="20" t="inlineStr">
         <is>
           <t>Frankreich</t>
         </is>
       </c>
-      <c r="L37" s="21" t="inlineStr">
+      <c r="L37" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="M37" s="21" t="inlineStr">
+      <c r="M37" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="N37" s="21" t="inlineStr">
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
